--- a/data/research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1574,8 +1574,824 @@
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>81d5e8fb055242d7</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>66955</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.592731</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>-0.0576186503496503</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:42.310322Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>7345625b0b914513</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.634473</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>-0.05592947678018578</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:44.213769Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>c8dcbeadf5b34699</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.53577</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>-0.05439393442622953</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:44.719266Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ea239d65f1f14f7b</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.703159</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.012756523219814242</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:45.283320Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>50e6494be67440f5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.746312</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.12654013688212928</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:45.864824Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>4b2b2f86991c437e</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.74664</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.046940300300300275</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:46.366525Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>d550f388bb4b466e</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.649674</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.059510065573770476</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:49.714123Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>4f55665fc05d46d9</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.501936</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>-0.04761354954954944</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:51.167478Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ10"/>
+  <autoFilter ref="A1:AJ18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2390,8 +2390,1640 @@
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>29cd5d7fb2e447d8</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>66955</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.592731</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>-0.0576186503496503</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:03.295097Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>6db2210bd2b94313</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.634473</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>-0.05592947678018578</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:05.251751Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>f8385c6f09db4a91</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.53577</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>-0.05439393442622953</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:05.753795Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>b3ba380b67d64b0c</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.703159</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.012756523219814242</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:06.296484Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>5ba2a2178c52408a</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.746312</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.12654013688212928</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:06.744519Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>4befe0e7f1d74620</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.74664</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0.046940300300300275</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:07.243416Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>9ba121a752924935</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.649674</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.059510065573770476</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:10.643274Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>a2413b5e99304865</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.501936</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>-0.028580431924882577</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:12.186730Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>aeb3e183924d4e34</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>66955</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.592731</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>-0.0576186503496503</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:02.304568Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ccc1e8e2e1d64cdd</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.634473</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>-0.05592947678018578</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:04.258724Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>31fbe8adcb214dbe</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.53577</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>-0.05439393442622953</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:04.775409Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>992591e290844289</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.703159</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.012756523219814242</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:05.228074Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>0553c963e8bf4775</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.746312</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.12654013688212928</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:05.711202Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>1d13d6877de84f43</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.74664</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.046940300300300275</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:06.165699Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>c151f983503f459e</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.649674</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.059510065573770476</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:09.518110Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>3861705137d34660</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.501936</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>-0.028580431924882577</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:10.958524Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ18"/>
+  <autoFilter ref="A1:AJ34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AJ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -742,14 +742,34 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>0.540000</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>0.000829</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>0.8547</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:34:43.998701Z</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="inlineStr"/>
       <c r="AF2" s="2" t="inlineStr"/>
@@ -4022,8 +4042,722 @@
       <c r="AI34" s="2" t="inlineStr"/>
       <c r="AJ34" s="2" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>0221e7c0b3ff415e</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.536074</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>-0.05408993442622945</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:16.193695Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>49173911fce94ab2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.634708</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>-0.05569447678018569</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:16.786728Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>72646e8e4be34673</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:17.281478Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>44a0fb44ecb24da0</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:17.851259Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>f89a6326bf8e4712</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:18.386531Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>cd540946225c4479</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:21.959634Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>079e3823ca774d99</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.502316</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>-0.016914769230769178</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:23.429810Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ34"/>
+  <autoFilter ref="A1:AJ41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ41"/>
+  <dimension ref="A1:AJ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4756,8 +4756,1436 @@
       <c r="AI41" s="2" t="inlineStr"/>
       <c r="AJ41" s="2" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>420673535e654aa4</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.536074</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>-0.05408993442622945</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:24.266645Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>b93543fef1f14165</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.634708</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>-0.05569447678018569</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:24.776615Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>45861ba1c87e4556</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:25.287120Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>d598b2956bc34a33</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:25.777893Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>69e4b819102047aa</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:26.282734Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>f8160aed0a7540c3</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:29.638928Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>5788f3fe8fbc47bb</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.502316</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>-0.007487921568627431</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:31.198418Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>3ff75cd83cbd4604</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.536074</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>-0.05408993442622945</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:16.992475Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>f9871da3cc61401b</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.634708</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>-0.05569447678018569</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:17.534127Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>3abaa2e5212747e8</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:18.085863Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>d56a8758b5464fb4</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:18.584911Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>9028b0dcde5a4be8</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:19.163906Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>160193c737134870</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:22.895388Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>b3f0574ef0f34113</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.502316</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>-0.007487921568627431</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:24.464493Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ41"/>
+  <autoFilter ref="A1:AJ55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ55"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6184,8 +6184,824 @@
       <c r="AI55" s="2" t="inlineStr"/>
       <c r="AJ55" s="2" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>8230b4f561334d53</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.536074</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>-0.05408993442622945</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:08.792428Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>3edfe2a9d6af41a8</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.634708</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>-0.05569447678018569</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:09.253322Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>0ffc76eff5624ce8</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:09.781954Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>45dad91979bf4424</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.279453Z</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>118937b8f1714152</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.786284Z</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>b5fe5d6991554d72</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:14.243617Z</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>a66cf328e22945cd</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>67938</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>0.62116</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>-0.07853969969969965</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:14.766196Z</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>142c09ce36804da0</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>0.502316</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>-0.007487921568627431</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:15.724362Z</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ55"/>
+  <autoFilter ref="A1:AJ63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$417</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ337"/>
+  <dimension ref="A1:AJ417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -35128,8 +35128,8168 @@
       <c r="AI337" s="2" t="inlineStr"/>
       <c r="AJ337" s="2" t="inlineStr"/>
     </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>07863d82d2f64af4</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>70669</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr">
+        <is>
+          <t>0.530268</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="inlineStr"/>
+      <c r="N338" s="2" t="inlineStr"/>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="inlineStr"/>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>-0.008902506912442432</t>
+        </is>
+      </c>
+      <c r="R338" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:18.693939Z</t>
+        </is>
+      </c>
+      <c r="S338" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="T338" s="2" t="inlineStr"/>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr"/>
+      <c r="W338" s="2" t="inlineStr"/>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr"/>
+      <c r="AB338" s="2" t="inlineStr"/>
+      <c r="AC338" s="2" t="inlineStr"/>
+      <c r="AD338" s="2" t="inlineStr"/>
+      <c r="AE338" s="2" t="inlineStr"/>
+      <c r="AF338" s="2" t="inlineStr"/>
+      <c r="AG338" s="2" t="inlineStr"/>
+      <c r="AH338" s="2" t="inlineStr"/>
+      <c r="AI338" s="2" t="inlineStr"/>
+      <c r="AJ338" s="2" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>416fb62e3b204556</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>68284</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>0.613874</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr"/>
+      <c r="N339" s="2" t="inlineStr"/>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="inlineStr"/>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>-0.06663718210862613</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:20.560660Z</t>
+        </is>
+      </c>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr"/>
+      <c r="W339" s="2" t="inlineStr"/>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr"/>
+      <c r="AB339" s="2" t="inlineStr"/>
+      <c r="AC339" s="2" t="inlineStr"/>
+      <c r="AD339" s="2" t="inlineStr"/>
+      <c r="AE339" s="2" t="inlineStr"/>
+      <c r="AF339" s="2" t="inlineStr"/>
+      <c r="AG339" s="2" t="inlineStr"/>
+      <c r="AH339" s="2" t="inlineStr"/>
+      <c r="AI339" s="2" t="inlineStr"/>
+      <c r="AJ339" s="2" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>c8a2f10b7e634d4f</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>68295</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>0.578292</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr"/>
+      <c r="N340" s="2" t="inlineStr"/>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr"/>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>-0.02170800000000006</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:21.145157Z</t>
+        </is>
+      </c>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="inlineStr"/>
+      <c r="U340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="inlineStr"/>
+      <c r="W340" s="2" t="inlineStr"/>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr"/>
+      <c r="AA340" s="2" t="inlineStr"/>
+      <c r="AB340" s="2" t="inlineStr"/>
+      <c r="AC340" s="2" t="inlineStr"/>
+      <c r="AD340" s="2" t="inlineStr"/>
+      <c r="AE340" s="2" t="inlineStr"/>
+      <c r="AF340" s="2" t="inlineStr"/>
+      <c r="AG340" s="2" t="inlineStr"/>
+      <c r="AH340" s="2" t="inlineStr"/>
+      <c r="AI340" s="2" t="inlineStr"/>
+      <c r="AJ340" s="2" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>85ae1f72de1d4767</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>68510</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>0.517061</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr"/>
+      <c r="N341" s="2" t="inlineStr"/>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr"/>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>-0.09231400000000001</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:23.581088Z</t>
+        </is>
+      </c>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr"/>
+      <c r="U341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="inlineStr"/>
+      <c r="W341" s="2" t="inlineStr"/>
+      <c r="X341" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Z341" s="2" t="inlineStr"/>
+      <c r="AA341" s="2" t="inlineStr"/>
+      <c r="AB341" s="2" t="inlineStr"/>
+      <c r="AC341" s="2" t="inlineStr"/>
+      <c r="AD341" s="2" t="inlineStr"/>
+      <c r="AE341" s="2" t="inlineStr"/>
+      <c r="AF341" s="2" t="inlineStr"/>
+      <c r="AG341" s="2" t="inlineStr"/>
+      <c r="AH341" s="2" t="inlineStr"/>
+      <c r="AI341" s="2" t="inlineStr"/>
+      <c r="AJ341" s="2" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>5a3f2428cd894478</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K342" s="2" t="inlineStr"/>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>0.631317</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr"/>
+      <c r="N342" s="2" t="inlineStr"/>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="inlineStr"/>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>0.1215130784313726</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:24.115171Z</t>
+        </is>
+      </c>
+      <c r="S342" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T342" s="2" t="inlineStr"/>
+      <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr"/>
+      <c r="W342" s="2" t="inlineStr"/>
+      <c r="X342" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y342" s="2" t="inlineStr"/>
+      <c r="Z342" s="2" t="inlineStr"/>
+      <c r="AA342" s="2" t="inlineStr"/>
+      <c r="AB342" s="2" t="inlineStr"/>
+      <c r="AC342" s="2" t="inlineStr"/>
+      <c r="AD342" s="2" t="inlineStr"/>
+      <c r="AE342" s="2" t="inlineStr"/>
+      <c r="AF342" s="2" t="inlineStr"/>
+      <c r="AG342" s="2" t="inlineStr"/>
+      <c r="AH342" s="2" t="inlineStr"/>
+      <c r="AI342" s="2" t="inlineStr"/>
+      <c r="AJ342" s="2" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>3deb2e8ca87a4605</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>70567</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K343" s="2" t="inlineStr"/>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>0.518338</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr"/>
+      <c r="N343" s="2" t="inlineStr"/>
+      <c r="O343" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="inlineStr"/>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>0.13810986311787066</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:26.492607Z</t>
+        </is>
+      </c>
+      <c r="S343" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T343" s="2" t="inlineStr"/>
+      <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr"/>
+      <c r="W343" s="2" t="inlineStr"/>
+      <c r="X343" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y343" s="2" t="inlineStr"/>
+      <c r="Z343" s="2" t="inlineStr"/>
+      <c r="AA343" s="2" t="inlineStr"/>
+      <c r="AB343" s="2" t="inlineStr"/>
+      <c r="AC343" s="2" t="inlineStr"/>
+      <c r="AD343" s="2" t="inlineStr"/>
+      <c r="AE343" s="2" t="inlineStr"/>
+      <c r="AF343" s="2" t="inlineStr"/>
+      <c r="AG343" s="2" t="inlineStr"/>
+      <c r="AH343" s="2" t="inlineStr"/>
+      <c r="AI343" s="2" t="inlineStr"/>
+      <c r="AJ343" s="2" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2c3e35a1ac53477c</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>68691</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K344" s="2" t="inlineStr"/>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>0.549366</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr"/>
+      <c r="N344" s="2" t="inlineStr"/>
+      <c r="O344" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P344" s="2" t="inlineStr"/>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>-0.12060099669966995</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:27.684417Z</t>
+        </is>
+      </c>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="inlineStr"/>
+      <c r="V344" s="2" t="inlineStr"/>
+      <c r="W344" s="2" t="inlineStr"/>
+      <c r="X344" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y344" s="2" t="inlineStr"/>
+      <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr"/>
+      <c r="AB344" s="2" t="inlineStr"/>
+      <c r="AC344" s="2" t="inlineStr"/>
+      <c r="AD344" s="2" t="inlineStr"/>
+      <c r="AE344" s="2" t="inlineStr"/>
+      <c r="AF344" s="2" t="inlineStr"/>
+      <c r="AG344" s="2" t="inlineStr"/>
+      <c r="AH344" s="2" t="inlineStr"/>
+      <c r="AI344" s="2" t="inlineStr"/>
+      <c r="AJ344" s="2" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>fcdceb275a3847b5</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>68689</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K345" s="2" t="inlineStr"/>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>0.573934</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr"/>
+      <c r="N345" s="2" t="inlineStr"/>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="inlineStr"/>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>-0.026066000000000034</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:28.233054Z</t>
+        </is>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="inlineStr"/>
+      <c r="U345" s="2" t="inlineStr"/>
+      <c r="V345" s="2" t="inlineStr"/>
+      <c r="W345" s="2" t="inlineStr"/>
+      <c r="X345" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y345" s="2" t="inlineStr"/>
+      <c r="Z345" s="2" t="inlineStr"/>
+      <c r="AA345" s="2" t="inlineStr"/>
+      <c r="AB345" s="2" t="inlineStr"/>
+      <c r="AC345" s="2" t="inlineStr"/>
+      <c r="AD345" s="2" t="inlineStr"/>
+      <c r="AE345" s="2" t="inlineStr"/>
+      <c r="AF345" s="2" t="inlineStr"/>
+      <c r="AG345" s="2" t="inlineStr"/>
+      <c r="AH345" s="2" t="inlineStr"/>
+      <c r="AI345" s="2" t="inlineStr"/>
+      <c r="AJ345" s="2" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>9ca822e16c0b4273</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>68688</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K346" s="2" t="inlineStr"/>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>0.531003</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr"/>
+      <c r="N346" s="2" t="inlineStr"/>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="inlineStr"/>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>-0.018546549549549485</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:28.891717Z</t>
+        </is>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr"/>
+      <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr"/>
+      <c r="W346" s="2" t="inlineStr"/>
+      <c r="X346" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y346" s="2" t="inlineStr"/>
+      <c r="Z346" s="2" t="inlineStr"/>
+      <c r="AA346" s="2" t="inlineStr"/>
+      <c r="AB346" s="2" t="inlineStr"/>
+      <c r="AC346" s="2" t="inlineStr"/>
+      <c r="AD346" s="2" t="inlineStr"/>
+      <c r="AE346" s="2" t="inlineStr"/>
+      <c r="AF346" s="2" t="inlineStr"/>
+      <c r="AG346" s="2" t="inlineStr"/>
+      <c r="AH346" s="2" t="inlineStr"/>
+      <c r="AI346" s="2" t="inlineStr"/>
+      <c r="AJ346" s="2" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>9a5107422be749df</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K347" s="2" t="inlineStr"/>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>0.55055</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr"/>
+      <c r="N347" s="2" t="inlineStr"/>
+      <c r="O347" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="inlineStr"/>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>0.01137949308755759</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:29.630272Z</t>
+        </is>
+      </c>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="inlineStr"/>
+      <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr"/>
+      <c r="W347" s="2" t="inlineStr"/>
+      <c r="X347" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr"/>
+      <c r="AA347" s="2" t="inlineStr"/>
+      <c r="AB347" s="2" t="inlineStr"/>
+      <c r="AC347" s="2" t="inlineStr"/>
+      <c r="AD347" s="2" t="inlineStr"/>
+      <c r="AE347" s="2" t="inlineStr"/>
+      <c r="AF347" s="2" t="inlineStr"/>
+      <c r="AG347" s="2" t="inlineStr"/>
+      <c r="AH347" s="2" t="inlineStr"/>
+      <c r="AI347" s="2" t="inlineStr"/>
+      <c r="AJ347" s="2" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>e5cfadf89cfd4eba</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="inlineStr"/>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>0.624143</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr"/>
+      <c r="N348" s="2" t="inlineStr"/>
+      <c r="O348" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="inlineStr"/>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>0.004371136882129312</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:32.661629Z</t>
+        </is>
+      </c>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T348" s="2" t="inlineStr"/>
+      <c r="U348" s="2" t="inlineStr"/>
+      <c r="V348" s="2" t="inlineStr"/>
+      <c r="W348" s="2" t="inlineStr"/>
+      <c r="X348" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y348" s="2" t="inlineStr"/>
+      <c r="Z348" s="2" t="inlineStr"/>
+      <c r="AA348" s="2" t="inlineStr"/>
+      <c r="AB348" s="2" t="inlineStr"/>
+      <c r="AC348" s="2" t="inlineStr"/>
+      <c r="AD348" s="2" t="inlineStr"/>
+      <c r="AE348" s="2" t="inlineStr"/>
+      <c r="AF348" s="2" t="inlineStr"/>
+      <c r="AG348" s="2" t="inlineStr"/>
+      <c r="AH348" s="2" t="inlineStr"/>
+      <c r="AI348" s="2" t="inlineStr"/>
+      <c r="AJ348" s="2" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>879c6e7d25254afd</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K349" s="2" t="inlineStr"/>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>0.591618</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr"/>
+      <c r="N349" s="2" t="inlineStr"/>
+      <c r="O349" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="inlineStr"/>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>0.1624334506437768</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:33.243967Z</t>
+        </is>
+      </c>
+      <c r="S349" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T349" s="2" t="inlineStr"/>
+      <c r="U349" s="2" t="inlineStr"/>
+      <c r="V349" s="2" t="inlineStr"/>
+      <c r="W349" s="2" t="inlineStr"/>
+      <c r="X349" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y349" s="2" t="inlineStr"/>
+      <c r="Z349" s="2" t="inlineStr"/>
+      <c r="AA349" s="2" t="inlineStr"/>
+      <c r="AB349" s="2" t="inlineStr"/>
+      <c r="AC349" s="2" t="inlineStr"/>
+      <c r="AD349" s="2" t="inlineStr"/>
+      <c r="AE349" s="2" t="inlineStr"/>
+      <c r="AF349" s="2" t="inlineStr"/>
+      <c r="AG349" s="2" t="inlineStr"/>
+      <c r="AH349" s="2" t="inlineStr"/>
+      <c r="AI349" s="2" t="inlineStr"/>
+      <c r="AJ349" s="2" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>8874e0edaca64047</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>69141</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K350" s="2" t="inlineStr"/>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>0.649994</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr"/>
+      <c r="N350" s="2" t="inlineStr"/>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="inlineStr"/>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>-0.00035565034965034936</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:33.953532Z</t>
+        </is>
+      </c>
+      <c r="S350" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T350" s="2" t="inlineStr"/>
+      <c r="U350" s="2" t="inlineStr"/>
+      <c r="V350" s="2" t="inlineStr"/>
+      <c r="W350" s="2" t="inlineStr"/>
+      <c r="X350" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y350" s="2" t="inlineStr"/>
+      <c r="Z350" s="2" t="inlineStr"/>
+      <c r="AA350" s="2" t="inlineStr"/>
+      <c r="AB350" s="2" t="inlineStr"/>
+      <c r="AC350" s="2" t="inlineStr"/>
+      <c r="AD350" s="2" t="inlineStr"/>
+      <c r="AE350" s="2" t="inlineStr"/>
+      <c r="AF350" s="2" t="inlineStr"/>
+      <c r="AG350" s="2" t="inlineStr"/>
+      <c r="AH350" s="2" t="inlineStr"/>
+      <c r="AI350" s="2" t="inlineStr"/>
+      <c r="AJ350" s="2" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>875af41028484982</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>69234</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K351" s="2" t="inlineStr"/>
+      <c r="L351" s="2" t="inlineStr">
+        <is>
+          <t>0.51668</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="inlineStr"/>
+      <c r="N351" s="2" t="inlineStr"/>
+      <c r="O351" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P351" s="2" t="inlineStr"/>
+      <c r="Q351" s="2" t="inlineStr">
+        <is>
+          <t>0.1670296503496504</t>
+        </is>
+      </c>
+      <c r="R351" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:34.470540Z</t>
+        </is>
+      </c>
+      <c r="S351" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T351" s="2" t="inlineStr"/>
+      <c r="U351" s="2" t="inlineStr"/>
+      <c r="V351" s="2" t="inlineStr"/>
+      <c r="W351" s="2" t="inlineStr"/>
+      <c r="X351" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y351" s="2" t="inlineStr"/>
+      <c r="Z351" s="2" t="inlineStr"/>
+      <c r="AA351" s="2" t="inlineStr"/>
+      <c r="AB351" s="2" t="inlineStr"/>
+      <c r="AC351" s="2" t="inlineStr"/>
+      <c r="AD351" s="2" t="inlineStr"/>
+      <c r="AE351" s="2" t="inlineStr"/>
+      <c r="AF351" s="2" t="inlineStr"/>
+      <c r="AG351" s="2" t="inlineStr"/>
+      <c r="AH351" s="2" t="inlineStr"/>
+      <c r="AI351" s="2" t="inlineStr"/>
+      <c r="AJ351" s="2" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2d7a8750fa7441be</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>69233</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K352" s="2" t="inlineStr"/>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>0.5725</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr"/>
+      <c r="N352" s="2" t="inlineStr"/>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr"/>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>0.2323639455782313</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:35.140661Z</t>
+        </is>
+      </c>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="inlineStr"/>
+      <c r="U352" s="2" t="inlineStr"/>
+      <c r="V352" s="2" t="inlineStr"/>
+      <c r="W352" s="2" t="inlineStr"/>
+      <c r="X352" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y352" s="2" t="inlineStr"/>
+      <c r="Z352" s="2" t="inlineStr"/>
+      <c r="AA352" s="2" t="inlineStr"/>
+      <c r="AB352" s="2" t="inlineStr"/>
+      <c r="AC352" s="2" t="inlineStr"/>
+      <c r="AD352" s="2" t="inlineStr"/>
+      <c r="AE352" s="2" t="inlineStr"/>
+      <c r="AF352" s="2" t="inlineStr"/>
+      <c r="AG352" s="2" t="inlineStr"/>
+      <c r="AH352" s="2" t="inlineStr"/>
+      <c r="AI352" s="2" t="inlineStr"/>
+      <c r="AJ352" s="2" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>29d0ac8f079b4574</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K353" s="2" t="inlineStr"/>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>0.604656</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr"/>
+      <c r="N353" s="2" t="inlineStr"/>
+      <c r="O353" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="inlineStr"/>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>0.03384054935622316</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:35.709175Z</t>
+        </is>
+      </c>
+      <c r="S353" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T353" s="2" t="inlineStr"/>
+      <c r="U353" s="2" t="inlineStr"/>
+      <c r="V353" s="2" t="inlineStr"/>
+      <c r="W353" s="2" t="inlineStr"/>
+      <c r="X353" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y353" s="2" t="inlineStr"/>
+      <c r="Z353" s="2" t="inlineStr"/>
+      <c r="AA353" s="2" t="inlineStr"/>
+      <c r="AB353" s="2" t="inlineStr"/>
+      <c r="AC353" s="2" t="inlineStr"/>
+      <c r="AD353" s="2" t="inlineStr"/>
+      <c r="AE353" s="2" t="inlineStr"/>
+      <c r="AF353" s="2" t="inlineStr"/>
+      <c r="AG353" s="2" t="inlineStr"/>
+      <c r="AH353" s="2" t="inlineStr"/>
+      <c r="AI353" s="2" t="inlineStr"/>
+      <c r="AJ353" s="2" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>f2c0ecf4a1834c1f</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>69304</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K354" s="2" t="inlineStr"/>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>0.546359</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr"/>
+      <c r="N354" s="2" t="inlineStr"/>
+      <c r="O354" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="inlineStr"/>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>0.03655507843137262</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:36.280064Z</t>
+        </is>
+      </c>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="inlineStr"/>
+      <c r="U354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="inlineStr"/>
+      <c r="W354" s="2" t="inlineStr"/>
+      <c r="X354" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y354" s="2" t="inlineStr"/>
+      <c r="Z354" s="2" t="inlineStr"/>
+      <c r="AA354" s="2" t="inlineStr"/>
+      <c r="AB354" s="2" t="inlineStr"/>
+      <c r="AC354" s="2" t="inlineStr"/>
+      <c r="AD354" s="2" t="inlineStr"/>
+      <c r="AE354" s="2" t="inlineStr"/>
+      <c r="AF354" s="2" t="inlineStr"/>
+      <c r="AG354" s="2" t="inlineStr"/>
+      <c r="AH354" s="2" t="inlineStr"/>
+      <c r="AI354" s="2" t="inlineStr"/>
+      <c r="AJ354" s="2" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>79699550346e455c</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>69507</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K355" s="2" t="inlineStr"/>
+      <c r="L355" s="2" t="inlineStr">
+        <is>
+          <t>0.638913</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="inlineStr"/>
+      <c r="N355" s="2" t="inlineStr"/>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="inlineStr"/>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>0.05908106722689077</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:37.478514Z</t>
+        </is>
+      </c>
+      <c r="S355" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T355" s="2" t="inlineStr"/>
+      <c r="U355" s="2" t="inlineStr"/>
+      <c r="V355" s="2" t="inlineStr"/>
+      <c r="W355" s="2" t="inlineStr"/>
+      <c r="X355" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y355" s="2" t="inlineStr"/>
+      <c r="Z355" s="2" t="inlineStr"/>
+      <c r="AA355" s="2" t="inlineStr"/>
+      <c r="AB355" s="2" t="inlineStr"/>
+      <c r="AC355" s="2" t="inlineStr"/>
+      <c r="AD355" s="2" t="inlineStr"/>
+      <c r="AE355" s="2" t="inlineStr"/>
+      <c r="AF355" s="2" t="inlineStr"/>
+      <c r="AG355" s="2" t="inlineStr"/>
+      <c r="AH355" s="2" t="inlineStr"/>
+      <c r="AI355" s="2" t="inlineStr"/>
+      <c r="AJ355" s="2" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>445f6627fb0c4a12</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>69506</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K356" s="2" t="inlineStr"/>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>0.597302</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr"/>
+      <c r="N356" s="2" t="inlineStr"/>
+      <c r="O356" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="inlineStr"/>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>0.1874659344262295</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:38.198370Z</t>
+        </is>
+      </c>
+      <c r="S356" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="inlineStr"/>
+      <c r="V356" s="2" t="inlineStr"/>
+      <c r="W356" s="2" t="inlineStr"/>
+      <c r="X356" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y356" s="2" t="inlineStr"/>
+      <c r="Z356" s="2" t="inlineStr"/>
+      <c r="AA356" s="2" t="inlineStr"/>
+      <c r="AB356" s="2" t="inlineStr"/>
+      <c r="AC356" s="2" t="inlineStr"/>
+      <c r="AD356" s="2" t="inlineStr"/>
+      <c r="AE356" s="2" t="inlineStr"/>
+      <c r="AF356" s="2" t="inlineStr"/>
+      <c r="AG356" s="2" t="inlineStr"/>
+      <c r="AH356" s="2" t="inlineStr"/>
+      <c r="AI356" s="2" t="inlineStr"/>
+      <c r="AJ356" s="2" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>e619060d264f4591</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>69512</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K357" s="2" t="inlineStr"/>
+      <c r="L357" s="2" t="inlineStr">
+        <is>
+          <t>0.739915</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="inlineStr"/>
+      <c r="N357" s="2" t="inlineStr"/>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="inlineStr"/>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>0.04951252321981425</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:38.799435Z</t>
+        </is>
+      </c>
+      <c r="S357" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="inlineStr"/>
+      <c r="V357" s="2" t="inlineStr"/>
+      <c r="W357" s="2" t="inlineStr"/>
+      <c r="X357" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y357" s="2" t="inlineStr"/>
+      <c r="Z357" s="2" t="inlineStr"/>
+      <c r="AA357" s="2" t="inlineStr"/>
+      <c r="AB357" s="2" t="inlineStr"/>
+      <c r="AC357" s="2" t="inlineStr"/>
+      <c r="AD357" s="2" t="inlineStr"/>
+      <c r="AE357" s="2" t="inlineStr"/>
+      <c r="AF357" s="2" t="inlineStr"/>
+      <c r="AG357" s="2" t="inlineStr"/>
+      <c r="AH357" s="2" t="inlineStr"/>
+      <c r="AI357" s="2" t="inlineStr"/>
+      <c r="AJ357" s="2" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>8583a63002f640fa</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>69511</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K358" s="2" t="inlineStr"/>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>0.699554</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr"/>
+      <c r="N358" s="2" t="inlineStr"/>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="inlineStr"/>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>0.09017900000000001</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:39.448018Z</t>
+        </is>
+      </c>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="inlineStr"/>
+      <c r="U358" s="2" t="inlineStr"/>
+      <c r="V358" s="2" t="inlineStr"/>
+      <c r="W358" s="2" t="inlineStr"/>
+      <c r="X358" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y358" s="2" t="inlineStr"/>
+      <c r="Z358" s="2" t="inlineStr"/>
+      <c r="AA358" s="2" t="inlineStr"/>
+      <c r="AB358" s="2" t="inlineStr"/>
+      <c r="AC358" s="2" t="inlineStr"/>
+      <c r="AD358" s="2" t="inlineStr"/>
+      <c r="AE358" s="2" t="inlineStr"/>
+      <c r="AF358" s="2" t="inlineStr"/>
+      <c r="AG358" s="2" t="inlineStr"/>
+      <c r="AH358" s="2" t="inlineStr"/>
+      <c r="AI358" s="2" t="inlineStr"/>
+      <c r="AJ358" s="2" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>946a1123a85b45a6</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>69539</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K359" s="2" t="inlineStr"/>
+      <c r="L359" s="2" t="inlineStr">
+        <is>
+          <t>0.637225</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="inlineStr"/>
+      <c r="N359" s="2" t="inlineStr"/>
+      <c r="O359" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="inlineStr"/>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>0.0777536343612335</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:40.623507Z</t>
+        </is>
+      </c>
+      <c r="S359" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T359" s="2" t="inlineStr"/>
+      <c r="U359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="inlineStr"/>
+      <c r="W359" s="2" t="inlineStr"/>
+      <c r="X359" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y359" s="2" t="inlineStr"/>
+      <c r="Z359" s="2" t="inlineStr"/>
+      <c r="AA359" s="2" t="inlineStr"/>
+      <c r="AB359" s="2" t="inlineStr"/>
+      <c r="AC359" s="2" t="inlineStr"/>
+      <c r="AD359" s="2" t="inlineStr"/>
+      <c r="AE359" s="2" t="inlineStr"/>
+      <c r="AF359" s="2" t="inlineStr"/>
+      <c r="AG359" s="2" t="inlineStr"/>
+      <c r="AH359" s="2" t="inlineStr"/>
+      <c r="AI359" s="2" t="inlineStr"/>
+      <c r="AJ359" s="2" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>a2bf5ed6c7794033</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="2" t="inlineStr">
+        <is>
+          <t>0.665588</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="inlineStr"/>
+      <c r="N360" s="2" t="inlineStr"/>
+      <c r="O360" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P360" s="2" t="inlineStr"/>
+      <c r="Q360" s="2" t="inlineStr">
+        <is>
+          <t>0.10611663436123342</t>
+        </is>
+      </c>
+      <c r="R360" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:45.008665Z</t>
+        </is>
+      </c>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="inlineStr"/>
+      <c r="U360" s="2" t="inlineStr"/>
+      <c r="V360" s="2" t="inlineStr"/>
+      <c r="W360" s="2" t="inlineStr"/>
+      <c r="X360" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y360" s="2" t="inlineStr"/>
+      <c r="Z360" s="2" t="inlineStr"/>
+      <c r="AA360" s="2" t="inlineStr"/>
+      <c r="AB360" s="2" t="inlineStr"/>
+      <c r="AC360" s="2" t="inlineStr"/>
+      <c r="AD360" s="2" t="inlineStr"/>
+      <c r="AE360" s="2" t="inlineStr"/>
+      <c r="AF360" s="2" t="inlineStr"/>
+      <c r="AG360" s="2" t="inlineStr"/>
+      <c r="AH360" s="2" t="inlineStr"/>
+      <c r="AI360" s="2" t="inlineStr"/>
+      <c r="AJ360" s="2" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>a368efdb81284e5a</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>69817</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K361" s="2" t="inlineStr"/>
+      <c r="L361" s="2" t="inlineStr">
+        <is>
+          <t>0.560327</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="inlineStr"/>
+      <c r="N361" s="2" t="inlineStr"/>
+      <c r="O361" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="inlineStr"/>
+      <c r="Q361" s="2" t="inlineStr">
+        <is>
+          <t>0.06032700000000002</t>
+        </is>
+      </c>
+      <c r="R361" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:45.501478Z</t>
+        </is>
+      </c>
+      <c r="S361" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T361" s="2" t="inlineStr"/>
+      <c r="U361" s="2" t="inlineStr"/>
+      <c r="V361" s="2" t="inlineStr"/>
+      <c r="W361" s="2" t="inlineStr"/>
+      <c r="X361" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y361" s="2" t="inlineStr"/>
+      <c r="Z361" s="2" t="inlineStr"/>
+      <c r="AA361" s="2" t="inlineStr"/>
+      <c r="AB361" s="2" t="inlineStr"/>
+      <c r="AC361" s="2" t="inlineStr"/>
+      <c r="AD361" s="2" t="inlineStr"/>
+      <c r="AE361" s="2" t="inlineStr"/>
+      <c r="AF361" s="2" t="inlineStr"/>
+      <c r="AG361" s="2" t="inlineStr"/>
+      <c r="AH361" s="2" t="inlineStr"/>
+      <c r="AI361" s="2" t="inlineStr"/>
+      <c r="AJ361" s="2" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>17c713c0fa9e452a</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>69818</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K362" s="2" t="inlineStr"/>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>0.530077</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="inlineStr"/>
+      <c r="N362" s="2" t="inlineStr"/>
+      <c r="O362" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P362" s="2" t="inlineStr"/>
+      <c r="Q362" s="2" t="inlineStr">
+        <is>
+          <t>0.10990893277310926</t>
+        </is>
+      </c>
+      <c r="R362" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:46.066957Z</t>
+        </is>
+      </c>
+      <c r="S362" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="inlineStr"/>
+      <c r="V362" s="2" t="inlineStr"/>
+      <c r="W362" s="2" t="inlineStr"/>
+      <c r="X362" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y362" s="2" t="inlineStr"/>
+      <c r="Z362" s="2" t="inlineStr"/>
+      <c r="AA362" s="2" t="inlineStr"/>
+      <c r="AB362" s="2" t="inlineStr"/>
+      <c r="AC362" s="2" t="inlineStr"/>
+      <c r="AD362" s="2" t="inlineStr"/>
+      <c r="AE362" s="2" t="inlineStr"/>
+      <c r="AF362" s="2" t="inlineStr"/>
+      <c r="AG362" s="2" t="inlineStr"/>
+      <c r="AH362" s="2" t="inlineStr"/>
+      <c r="AI362" s="2" t="inlineStr"/>
+      <c r="AJ362" s="2" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>9205ec1daef94792</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>0.561203</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="inlineStr"/>
+      <c r="N363" s="2" t="inlineStr"/>
+      <c r="O363" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P363" s="2" t="inlineStr"/>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>0.12067436563876655</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:47.185518Z</t>
+        </is>
+      </c>
+      <c r="S363" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T363" s="2" t="inlineStr"/>
+      <c r="U363" s="2" t="inlineStr"/>
+      <c r="V363" s="2" t="inlineStr"/>
+      <c r="W363" s="2" t="inlineStr"/>
+      <c r="X363" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y363" s="2" t="inlineStr"/>
+      <c r="Z363" s="2" t="inlineStr"/>
+      <c r="AA363" s="2" t="inlineStr"/>
+      <c r="AB363" s="2" t="inlineStr"/>
+      <c r="AC363" s="2" t="inlineStr"/>
+      <c r="AD363" s="2" t="inlineStr"/>
+      <c r="AE363" s="2" t="inlineStr"/>
+      <c r="AF363" s="2" t="inlineStr"/>
+      <c r="AG363" s="2" t="inlineStr"/>
+      <c r="AH363" s="2" t="inlineStr"/>
+      <c r="AI363" s="2" t="inlineStr"/>
+      <c r="AJ363" s="2" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>26cd7a4ae9be4ce5</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>69870</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>0.55941</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="inlineStr"/>
+      <c r="N364" s="2" t="inlineStr"/>
+      <c r="O364" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="inlineStr"/>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>-0.02042193277310922</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:47.769046Z</t>
+        </is>
+      </c>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="inlineStr"/>
+      <c r="U364" s="2" t="inlineStr"/>
+      <c r="V364" s="2" t="inlineStr"/>
+      <c r="W364" s="2" t="inlineStr"/>
+      <c r="X364" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y364" s="2" t="inlineStr"/>
+      <c r="Z364" s="2" t="inlineStr"/>
+      <c r="AA364" s="2" t="inlineStr"/>
+      <c r="AB364" s="2" t="inlineStr"/>
+      <c r="AC364" s="2" t="inlineStr"/>
+      <c r="AD364" s="2" t="inlineStr"/>
+      <c r="AE364" s="2" t="inlineStr"/>
+      <c r="AF364" s="2" t="inlineStr"/>
+      <c r="AG364" s="2" t="inlineStr"/>
+      <c r="AH364" s="2" t="inlineStr"/>
+      <c r="AI364" s="2" t="inlineStr"/>
+      <c r="AJ364" s="2" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>4a0eab78c6394d30</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K365" s="2" t="inlineStr"/>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>0.832591</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr"/>
+      <c r="N365" s="2" t="inlineStr"/>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="inlineStr"/>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>0.24242706557377047</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:48.331322Z</t>
+        </is>
+      </c>
+      <c r="S365" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T365" s="2" t="inlineStr"/>
+      <c r="U365" s="2" t="inlineStr"/>
+      <c r="V365" s="2" t="inlineStr"/>
+      <c r="W365" s="2" t="inlineStr"/>
+      <c r="X365" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y365" s="2" t="inlineStr"/>
+      <c r="Z365" s="2" t="inlineStr"/>
+      <c r="AA365" s="2" t="inlineStr"/>
+      <c r="AB365" s="2" t="inlineStr"/>
+      <c r="AC365" s="2" t="inlineStr"/>
+      <c r="AD365" s="2" t="inlineStr"/>
+      <c r="AE365" s="2" t="inlineStr"/>
+      <c r="AF365" s="2" t="inlineStr"/>
+      <c r="AG365" s="2" t="inlineStr"/>
+      <c r="AH365" s="2" t="inlineStr"/>
+      <c r="AI365" s="2" t="inlineStr"/>
+      <c r="AJ365" s="2" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>790ff60420284858</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K366" s="2" t="inlineStr"/>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>0.577055</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr"/>
+      <c r="N366" s="2" t="inlineStr"/>
+      <c r="O366" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="inlineStr"/>
+      <c r="Q366" s="2" t="inlineStr">
+        <is>
+          <t>0.07705499999999998</t>
+        </is>
+      </c>
+      <c r="R366" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:48.838641Z</t>
+        </is>
+      </c>
+      <c r="S366" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="inlineStr"/>
+      <c r="W366" s="2" t="inlineStr"/>
+      <c r="X366" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y366" s="2" t="inlineStr"/>
+      <c r="Z366" s="2" t="inlineStr"/>
+      <c r="AA366" s="2" t="inlineStr"/>
+      <c r="AB366" s="2" t="inlineStr"/>
+      <c r="AC366" s="2" t="inlineStr"/>
+      <c r="AD366" s="2" t="inlineStr"/>
+      <c r="AE366" s="2" t="inlineStr"/>
+      <c r="AF366" s="2" t="inlineStr"/>
+      <c r="AG366" s="2" t="inlineStr"/>
+      <c r="AH366" s="2" t="inlineStr"/>
+      <c r="AI366" s="2" t="inlineStr"/>
+      <c r="AJ366" s="2" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>7fce0471e6234bd5</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>69930</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K367" s="2" t="inlineStr"/>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>0.536006</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr"/>
+      <c r="N367" s="2" t="inlineStr"/>
+      <c r="O367" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="inlineStr"/>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>0.08555554954954947</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:49.456329Z</t>
+        </is>
+      </c>
+      <c r="S367" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T367" s="2" t="inlineStr"/>
+      <c r="U367" s="2" t="inlineStr"/>
+      <c r="V367" s="2" t="inlineStr"/>
+      <c r="W367" s="2" t="inlineStr"/>
+      <c r="X367" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y367" s="2" t="inlineStr"/>
+      <c r="Z367" s="2" t="inlineStr"/>
+      <c r="AA367" s="2" t="inlineStr"/>
+      <c r="AB367" s="2" t="inlineStr"/>
+      <c r="AC367" s="2" t="inlineStr"/>
+      <c r="AD367" s="2" t="inlineStr"/>
+      <c r="AE367" s="2" t="inlineStr"/>
+      <c r="AF367" s="2" t="inlineStr"/>
+      <c r="AG367" s="2" t="inlineStr"/>
+      <c r="AH367" s="2" t="inlineStr"/>
+      <c r="AI367" s="2" t="inlineStr"/>
+      <c r="AJ367" s="2" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>f7f7793ec69647af</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>69951</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>0.516071</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr"/>
+      <c r="N368" s="2" t="inlineStr"/>
+      <c r="O368" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="inlineStr"/>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>0.13584286311787064</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:49.989456Z</t>
+        </is>
+      </c>
+      <c r="S368" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="inlineStr"/>
+      <c r="V368" s="2" t="inlineStr"/>
+      <c r="W368" s="2" t="inlineStr"/>
+      <c r="X368" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y368" s="2" t="inlineStr"/>
+      <c r="Z368" s="2" t="inlineStr"/>
+      <c r="AA368" s="2" t="inlineStr"/>
+      <c r="AB368" s="2" t="inlineStr"/>
+      <c r="AC368" s="2" t="inlineStr"/>
+      <c r="AD368" s="2" t="inlineStr"/>
+      <c r="AE368" s="2" t="inlineStr"/>
+      <c r="AF368" s="2" t="inlineStr"/>
+      <c r="AG368" s="2" t="inlineStr"/>
+      <c r="AH368" s="2" t="inlineStr"/>
+      <c r="AI368" s="2" t="inlineStr"/>
+      <c r="AJ368" s="2" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>4260705ad9db4735</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>69948</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K369" s="2" t="inlineStr"/>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>0.564089</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr"/>
+      <c r="N369" s="2" t="inlineStr"/>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="inlineStr"/>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>-0.07619876978417273</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:50.492012Z</t>
+        </is>
+      </c>
+      <c r="S369" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="inlineStr"/>
+      <c r="V369" s="2" t="inlineStr"/>
+      <c r="W369" s="2" t="inlineStr"/>
+      <c r="X369" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y369" s="2" t="inlineStr"/>
+      <c r="Z369" s="2" t="inlineStr"/>
+      <c r="AA369" s="2" t="inlineStr"/>
+      <c r="AB369" s="2" t="inlineStr"/>
+      <c r="AC369" s="2" t="inlineStr"/>
+      <c r="AD369" s="2" t="inlineStr"/>
+      <c r="AE369" s="2" t="inlineStr"/>
+      <c r="AF369" s="2" t="inlineStr"/>
+      <c r="AG369" s="2" t="inlineStr"/>
+      <c r="AH369" s="2" t="inlineStr"/>
+      <c r="AI369" s="2" t="inlineStr"/>
+      <c r="AJ369" s="2" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>51bbb45aa27f496d</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>69949</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K370" s="2" t="inlineStr"/>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>0.530192</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr"/>
+      <c r="N370" s="2" t="inlineStr"/>
+      <c r="O370" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P370" s="2" t="inlineStr"/>
+      <c r="Q370" s="2" t="inlineStr">
+        <is>
+          <t>-0.00032443192488262884</t>
+        </is>
+      </c>
+      <c r="R370" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:51.059933Z</t>
+        </is>
+      </c>
+      <c r="S370" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T370" s="2" t="inlineStr"/>
+      <c r="U370" s="2" t="inlineStr"/>
+      <c r="V370" s="2" t="inlineStr"/>
+      <c r="W370" s="2" t="inlineStr"/>
+      <c r="X370" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y370" s="2" t="inlineStr"/>
+      <c r="Z370" s="2" t="inlineStr"/>
+      <c r="AA370" s="2" t="inlineStr"/>
+      <c r="AB370" s="2" t="inlineStr"/>
+      <c r="AC370" s="2" t="inlineStr"/>
+      <c r="AD370" s="2" t="inlineStr"/>
+      <c r="AE370" s="2" t="inlineStr"/>
+      <c r="AF370" s="2" t="inlineStr"/>
+      <c r="AG370" s="2" t="inlineStr"/>
+      <c r="AH370" s="2" t="inlineStr"/>
+      <c r="AI370" s="2" t="inlineStr"/>
+      <c r="AJ370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>071c9e2b91ec42a0</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>69950</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>0.534563</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr"/>
+      <c r="N371" s="2" t="inlineStr"/>
+      <c r="O371" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P371" s="2" t="inlineStr"/>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>-0.08520886311787068</t>
+        </is>
+      </c>
+      <c r="R371" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:51.648091Z</t>
+        </is>
+      </c>
+      <c r="S371" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T371" s="2" t="inlineStr"/>
+      <c r="U371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="inlineStr"/>
+      <c r="W371" s="2" t="inlineStr"/>
+      <c r="X371" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y371" s="2" t="inlineStr"/>
+      <c r="Z371" s="2" t="inlineStr"/>
+      <c r="AA371" s="2" t="inlineStr"/>
+      <c r="AB371" s="2" t="inlineStr"/>
+      <c r="AC371" s="2" t="inlineStr"/>
+      <c r="AD371" s="2" t="inlineStr"/>
+      <c r="AE371" s="2" t="inlineStr"/>
+      <c r="AF371" s="2" t="inlineStr"/>
+      <c r="AG371" s="2" t="inlineStr"/>
+      <c r="AH371" s="2" t="inlineStr"/>
+      <c r="AI371" s="2" t="inlineStr"/>
+      <c r="AJ371" s="2" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>d3cb599a988a47b6</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>69952</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="inlineStr"/>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>0.525284</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="inlineStr"/>
+      <c r="N372" s="2" t="inlineStr"/>
+      <c r="O372" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P372" s="2" t="inlineStr"/>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>0.015480078431372557</t>
+        </is>
+      </c>
+      <c r="R372" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:52.154766Z</t>
+        </is>
+      </c>
+      <c r="S372" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="inlineStr"/>
+      <c r="U372" s="2" t="inlineStr"/>
+      <c r="V372" s="2" t="inlineStr"/>
+      <c r="W372" s="2" t="inlineStr"/>
+      <c r="X372" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y372" s="2" t="inlineStr"/>
+      <c r="Z372" s="2" t="inlineStr"/>
+      <c r="AA372" s="2" t="inlineStr"/>
+      <c r="AB372" s="2" t="inlineStr"/>
+      <c r="AC372" s="2" t="inlineStr"/>
+      <c r="AD372" s="2" t="inlineStr"/>
+      <c r="AE372" s="2" t="inlineStr"/>
+      <c r="AF372" s="2" t="inlineStr"/>
+      <c r="AG372" s="2" t="inlineStr"/>
+      <c r="AH372" s="2" t="inlineStr"/>
+      <c r="AI372" s="2" t="inlineStr"/>
+      <c r="AJ372" s="2" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>68b203c96d7949d3</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>0.607498</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr"/>
+      <c r="N373" s="2" t="inlineStr"/>
+      <c r="O373" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P373" s="2" t="inlineStr"/>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>0.09769407843137257</t>
+        </is>
+      </c>
+      <c r="R373" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:53.353991Z</t>
+        </is>
+      </c>
+      <c r="S373" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T373" s="2" t="inlineStr"/>
+      <c r="U373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="inlineStr"/>
+      <c r="W373" s="2" t="inlineStr"/>
+      <c r="X373" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y373" s="2" t="inlineStr"/>
+      <c r="Z373" s="2" t="inlineStr"/>
+      <c r="AA373" s="2" t="inlineStr"/>
+      <c r="AB373" s="2" t="inlineStr"/>
+      <c r="AC373" s="2" t="inlineStr"/>
+      <c r="AD373" s="2" t="inlineStr"/>
+      <c r="AE373" s="2" t="inlineStr"/>
+      <c r="AF373" s="2" t="inlineStr"/>
+      <c r="AG373" s="2" t="inlineStr"/>
+      <c r="AH373" s="2" t="inlineStr"/>
+      <c r="AI373" s="2" t="inlineStr"/>
+      <c r="AJ373" s="2" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>5619ca7fe11a4d71</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>70301</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="inlineStr"/>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>0.658548</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr"/>
+      <c r="N374" s="2" t="inlineStr"/>
+      <c r="O374" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P374" s="2" t="inlineStr"/>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>0.1777787692307693</t>
+        </is>
+      </c>
+      <c r="R374" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:53.849186Z</t>
+        </is>
+      </c>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr"/>
+      <c r="U374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="inlineStr"/>
+      <c r="W374" s="2" t="inlineStr"/>
+      <c r="X374" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y374" s="2" t="inlineStr"/>
+      <c r="Z374" s="2" t="inlineStr"/>
+      <c r="AA374" s="2" t="inlineStr"/>
+      <c r="AB374" s="2" t="inlineStr"/>
+      <c r="AC374" s="2" t="inlineStr"/>
+      <c r="AD374" s="2" t="inlineStr"/>
+      <c r="AE374" s="2" t="inlineStr"/>
+      <c r="AF374" s="2" t="inlineStr"/>
+      <c r="AG374" s="2" t="inlineStr"/>
+      <c r="AH374" s="2" t="inlineStr"/>
+      <c r="AI374" s="2" t="inlineStr"/>
+      <c r="AJ374" s="2" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>538c8fd33980445b</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>70302</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="inlineStr"/>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>0.535928</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr"/>
+      <c r="N375" s="2" t="inlineStr"/>
+      <c r="O375" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P375" s="2" t="inlineStr"/>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>-0.10435976978417272</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:54.466516Z</t>
+        </is>
+      </c>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="inlineStr"/>
+      <c r="U375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="inlineStr"/>
+      <c r="W375" s="2" t="inlineStr"/>
+      <c r="X375" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y375" s="2" t="inlineStr"/>
+      <c r="Z375" s="2" t="inlineStr"/>
+      <c r="AA375" s="2" t="inlineStr"/>
+      <c r="AB375" s="2" t="inlineStr"/>
+      <c r="AC375" s="2" t="inlineStr"/>
+      <c r="AD375" s="2" t="inlineStr"/>
+      <c r="AE375" s="2" t="inlineStr"/>
+      <c r="AF375" s="2" t="inlineStr"/>
+      <c r="AG375" s="2" t="inlineStr"/>
+      <c r="AH375" s="2" t="inlineStr"/>
+      <c r="AI375" s="2" t="inlineStr"/>
+      <c r="AJ375" s="2" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>761899155ab1481b</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>70349</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K376" s="2" t="inlineStr"/>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>0.649617</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr"/>
+      <c r="N376" s="2" t="inlineStr"/>
+      <c r="O376" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P376" s="2" t="inlineStr"/>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>-0.030894182108626156</t>
+        </is>
+      </c>
+      <c r="R376" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:55.761206Z</t>
+        </is>
+      </c>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr"/>
+      <c r="U376" s="2" t="inlineStr"/>
+      <c r="V376" s="2" t="inlineStr"/>
+      <c r="W376" s="2" t="inlineStr"/>
+      <c r="X376" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y376" s="2" t="inlineStr"/>
+      <c r="Z376" s="2" t="inlineStr"/>
+      <c r="AA376" s="2" t="inlineStr"/>
+      <c r="AB376" s="2" t="inlineStr"/>
+      <c r="AC376" s="2" t="inlineStr"/>
+      <c r="AD376" s="2" t="inlineStr"/>
+      <c r="AE376" s="2" t="inlineStr"/>
+      <c r="AF376" s="2" t="inlineStr"/>
+      <c r="AG376" s="2" t="inlineStr"/>
+      <c r="AH376" s="2" t="inlineStr"/>
+      <c r="AI376" s="2" t="inlineStr"/>
+      <c r="AJ376" s="2" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>200a77973f404e98</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>70348</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K377" s="2" t="inlineStr"/>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>0.500208</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr"/>
+      <c r="N377" s="2" t="inlineStr"/>
+      <c r="O377" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P377" s="2" t="inlineStr"/>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>-0.18030318210862617</t>
+        </is>
+      </c>
+      <c r="R377" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:56.328221Z</t>
+        </is>
+      </c>
+      <c r="S377" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="inlineStr"/>
+      <c r="U377" s="2" t="inlineStr"/>
+      <c r="V377" s="2" t="inlineStr"/>
+      <c r="W377" s="2" t="inlineStr"/>
+      <c r="X377" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y377" s="2" t="inlineStr"/>
+      <c r="Z377" s="2" t="inlineStr"/>
+      <c r="AA377" s="2" t="inlineStr"/>
+      <c r="AB377" s="2" t="inlineStr"/>
+      <c r="AC377" s="2" t="inlineStr"/>
+      <c r="AD377" s="2" t="inlineStr"/>
+      <c r="AE377" s="2" t="inlineStr"/>
+      <c r="AF377" s="2" t="inlineStr"/>
+      <c r="AG377" s="2" t="inlineStr"/>
+      <c r="AH377" s="2" t="inlineStr"/>
+      <c r="AI377" s="2" t="inlineStr"/>
+      <c r="AJ377" s="2" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>fc336818cab644d3</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="inlineStr"/>
+      <c r="L378" s="2" t="inlineStr">
+        <is>
+          <t>0.566884</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="inlineStr"/>
+      <c r="N378" s="2" t="inlineStr"/>
+      <c r="O378" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P378" s="2" t="inlineStr"/>
+      <c r="Q378" s="2" t="inlineStr">
+        <is>
+          <t>-0.012947932773109128</t>
+        </is>
+      </c>
+      <c r="R378" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:56.926613Z</t>
+        </is>
+      </c>
+      <c r="S378" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T378" s="2" t="inlineStr"/>
+      <c r="U378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="inlineStr"/>
+      <c r="W378" s="2" t="inlineStr"/>
+      <c r="X378" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y378" s="2" t="inlineStr"/>
+      <c r="Z378" s="2" t="inlineStr"/>
+      <c r="AA378" s="2" t="inlineStr"/>
+      <c r="AB378" s="2" t="inlineStr"/>
+      <c r="AC378" s="2" t="inlineStr"/>
+      <c r="AD378" s="2" t="inlineStr"/>
+      <c r="AE378" s="2" t="inlineStr"/>
+      <c r="AF378" s="2" t="inlineStr"/>
+      <c r="AG378" s="2" t="inlineStr"/>
+      <c r="AH378" s="2" t="inlineStr"/>
+      <c r="AI378" s="2" t="inlineStr"/>
+      <c r="AJ378" s="2" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>8caa3b1c30fe41a5</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>70454</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K379" s="2" t="inlineStr"/>
+      <c r="L379" s="2" t="inlineStr">
+        <is>
+          <t>0.515927</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="inlineStr"/>
+      <c r="N379" s="2" t="inlineStr"/>
+      <c r="O379" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P379" s="2" t="inlineStr"/>
+      <c r="Q379" s="2" t="inlineStr">
+        <is>
+          <t>-0.10384486311787067</t>
+        </is>
+      </c>
+      <c r="R379" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:58.149925Z</t>
+        </is>
+      </c>
+      <c r="S379" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T379" s="2" t="inlineStr"/>
+      <c r="U379" s="2" t="inlineStr"/>
+      <c r="V379" s="2" t="inlineStr"/>
+      <c r="W379" s="2" t="inlineStr"/>
+      <c r="X379" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y379" s="2" t="inlineStr"/>
+      <c r="Z379" s="2" t="inlineStr"/>
+      <c r="AA379" s="2" t="inlineStr"/>
+      <c r="AB379" s="2" t="inlineStr"/>
+      <c r="AC379" s="2" t="inlineStr"/>
+      <c r="AD379" s="2" t="inlineStr"/>
+      <c r="AE379" s="2" t="inlineStr"/>
+      <c r="AF379" s="2" t="inlineStr"/>
+      <c r="AG379" s="2" t="inlineStr"/>
+      <c r="AH379" s="2" t="inlineStr"/>
+      <c r="AI379" s="2" t="inlineStr"/>
+      <c r="AJ379" s="2" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>efbb276df1034e19</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="inlineStr"/>
+      <c r="L380" s="2" t="inlineStr">
+        <is>
+          <t>0.590765</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="inlineStr"/>
+      <c r="N380" s="2" t="inlineStr"/>
+      <c r="O380" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P380" s="2" t="inlineStr"/>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>0.0412154504504505</t>
+        </is>
+      </c>
+      <c r="R380" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:58.736471Z</t>
+        </is>
+      </c>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="inlineStr"/>
+      <c r="U380" s="2" t="inlineStr"/>
+      <c r="V380" s="2" t="inlineStr"/>
+      <c r="W380" s="2" t="inlineStr"/>
+      <c r="X380" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y380" s="2" t="inlineStr"/>
+      <c r="Z380" s="2" t="inlineStr"/>
+      <c r="AA380" s="2" t="inlineStr"/>
+      <c r="AB380" s="2" t="inlineStr"/>
+      <c r="AC380" s="2" t="inlineStr"/>
+      <c r="AD380" s="2" t="inlineStr"/>
+      <c r="AE380" s="2" t="inlineStr"/>
+      <c r="AF380" s="2" t="inlineStr"/>
+      <c r="AG380" s="2" t="inlineStr"/>
+      <c r="AH380" s="2" t="inlineStr"/>
+      <c r="AI380" s="2" t="inlineStr"/>
+      <c r="AJ380" s="2" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>a46bc66760264a71</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>68284</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="inlineStr"/>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>0.613874</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr"/>
+      <c r="N381" s="2" t="inlineStr"/>
+      <c r="O381" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="inlineStr"/>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>-0.0765284767801857</t>
+        </is>
+      </c>
+      <c r="R381" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:22.321845Z</t>
+        </is>
+      </c>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="inlineStr"/>
+      <c r="U381" s="2" t="inlineStr"/>
+      <c r="V381" s="2" t="inlineStr"/>
+      <c r="W381" s="2" t="inlineStr"/>
+      <c r="X381" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y381" s="2" t="inlineStr"/>
+      <c r="Z381" s="2" t="inlineStr"/>
+      <c r="AA381" s="2" t="inlineStr"/>
+      <c r="AB381" s="2" t="inlineStr"/>
+      <c r="AC381" s="2" t="inlineStr"/>
+      <c r="AD381" s="2" t="inlineStr"/>
+      <c r="AE381" s="2" t="inlineStr"/>
+      <c r="AF381" s="2" t="inlineStr"/>
+      <c r="AG381" s="2" t="inlineStr"/>
+      <c r="AH381" s="2" t="inlineStr"/>
+      <c r="AI381" s="2" t="inlineStr"/>
+      <c r="AJ381" s="2" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>6d7c0727a85f4b88</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>68295</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="inlineStr"/>
+      <c r="L382" s="2" t="inlineStr">
+        <is>
+          <t>0.578292</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="inlineStr"/>
+      <c r="N382" s="2" t="inlineStr"/>
+      <c r="O382" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P382" s="2" t="inlineStr"/>
+      <c r="Q382" s="2" t="inlineStr">
+        <is>
+          <t>-0.05133762962962951</t>
+        </is>
+      </c>
+      <c r="R382" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:22.857906Z</t>
+        </is>
+      </c>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr"/>
+      <c r="U382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="inlineStr"/>
+      <c r="W382" s="2" t="inlineStr"/>
+      <c r="X382" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y382" s="2" t="inlineStr"/>
+      <c r="Z382" s="2" t="inlineStr"/>
+      <c r="AA382" s="2" t="inlineStr"/>
+      <c r="AB382" s="2" t="inlineStr"/>
+      <c r="AC382" s="2" t="inlineStr"/>
+      <c r="AD382" s="2" t="inlineStr"/>
+      <c r="AE382" s="2" t="inlineStr"/>
+      <c r="AF382" s="2" t="inlineStr"/>
+      <c r="AG382" s="2" t="inlineStr"/>
+      <c r="AH382" s="2" t="inlineStr"/>
+      <c r="AI382" s="2" t="inlineStr"/>
+      <c r="AJ382" s="2" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>b564d3b9d1b2409f</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>68510</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K383" s="2" t="inlineStr"/>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>0.517061</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="inlineStr"/>
+      <c r="N383" s="2" t="inlineStr"/>
+      <c r="O383" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P383" s="2" t="inlineStr"/>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>0.10722493442622949</t>
+        </is>
+      </c>
+      <c r="R383" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:24.555143Z</t>
+        </is>
+      </c>
+      <c r="S383" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T383" s="2" t="inlineStr"/>
+      <c r="U383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="inlineStr"/>
+      <c r="W383" s="2" t="inlineStr"/>
+      <c r="X383" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y383" s="2" t="inlineStr"/>
+      <c r="Z383" s="2" t="inlineStr"/>
+      <c r="AA383" s="2" t="inlineStr"/>
+      <c r="AB383" s="2" t="inlineStr"/>
+      <c r="AC383" s="2" t="inlineStr"/>
+      <c r="AD383" s="2" t="inlineStr"/>
+      <c r="AE383" s="2" t="inlineStr"/>
+      <c r="AF383" s="2" t="inlineStr"/>
+      <c r="AG383" s="2" t="inlineStr"/>
+      <c r="AH383" s="2" t="inlineStr"/>
+      <c r="AI383" s="2" t="inlineStr"/>
+      <c r="AJ383" s="2" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>064213f3e4a84cb5</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K384" s="2" t="inlineStr"/>
+      <c r="L384" s="2" t="inlineStr">
+        <is>
+          <t>0.631317</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr"/>
+      <c r="O384" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P384" s="2" t="inlineStr"/>
+      <c r="Q384" s="2" t="inlineStr">
+        <is>
+          <t>0.11208623076923085</t>
+        </is>
+      </c>
+      <c r="R384" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:25.701342Z</t>
+        </is>
+      </c>
+      <c r="S384" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T384" s="2" t="inlineStr"/>
+      <c r="U384" s="2" t="inlineStr"/>
+      <c r="V384" s="2" t="inlineStr"/>
+      <c r="W384" s="2" t="inlineStr"/>
+      <c r="X384" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y384" s="2" t="inlineStr"/>
+      <c r="Z384" s="2" t="inlineStr"/>
+      <c r="AA384" s="2" t="inlineStr"/>
+      <c r="AB384" s="2" t="inlineStr"/>
+      <c r="AC384" s="2" t="inlineStr"/>
+      <c r="AD384" s="2" t="inlineStr"/>
+      <c r="AE384" s="2" t="inlineStr"/>
+      <c r="AF384" s="2" t="inlineStr"/>
+      <c r="AG384" s="2" t="inlineStr"/>
+      <c r="AH384" s="2" t="inlineStr"/>
+      <c r="AI384" s="2" t="inlineStr"/>
+      <c r="AJ384" s="2" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>69035b02241c4262</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>70567</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K385" s="2" t="inlineStr"/>
+      <c r="L385" s="2" t="inlineStr">
+        <is>
+          <t>0.518338</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="inlineStr"/>
+      <c r="N385" s="2" t="inlineStr"/>
+      <c r="O385" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P385" s="2" t="inlineStr"/>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>0.13810986311787066</t>
+        </is>
+      </c>
+      <c r="R385" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:26.316476Z</t>
+        </is>
+      </c>
+      <c r="S385" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T385" s="2" t="inlineStr"/>
+      <c r="U385" s="2" t="inlineStr"/>
+      <c r="V385" s="2" t="inlineStr"/>
+      <c r="W385" s="2" t="inlineStr"/>
+      <c r="X385" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y385" s="2" t="inlineStr"/>
+      <c r="Z385" s="2" t="inlineStr"/>
+      <c r="AA385" s="2" t="inlineStr"/>
+      <c r="AB385" s="2" t="inlineStr"/>
+      <c r="AC385" s="2" t="inlineStr"/>
+      <c r="AD385" s="2" t="inlineStr"/>
+      <c r="AE385" s="2" t="inlineStr"/>
+      <c r="AF385" s="2" t="inlineStr"/>
+      <c r="AG385" s="2" t="inlineStr"/>
+      <c r="AH385" s="2" t="inlineStr"/>
+      <c r="AI385" s="2" t="inlineStr"/>
+      <c r="AJ385" s="2" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>5bf1d28636384187</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>68691</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K386" s="2" t="inlineStr"/>
+      <c r="L386" s="2" t="inlineStr">
+        <is>
+          <t>0.549366</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr"/>
+      <c r="O386" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P386" s="2" t="inlineStr"/>
+      <c r="Q386" s="2" t="inlineStr">
+        <is>
+          <t>-0.12060099669966995</t>
+        </is>
+      </c>
+      <c r="R386" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:29.255997Z</t>
+        </is>
+      </c>
+      <c r="S386" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T386" s="2" t="inlineStr"/>
+      <c r="U386" s="2" t="inlineStr"/>
+      <c r="V386" s="2" t="inlineStr"/>
+      <c r="W386" s="2" t="inlineStr"/>
+      <c r="X386" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y386" s="2" t="inlineStr"/>
+      <c r="Z386" s="2" t="inlineStr"/>
+      <c r="AA386" s="2" t="inlineStr"/>
+      <c r="AB386" s="2" t="inlineStr"/>
+      <c r="AC386" s="2" t="inlineStr"/>
+      <c r="AD386" s="2" t="inlineStr"/>
+      <c r="AE386" s="2" t="inlineStr"/>
+      <c r="AF386" s="2" t="inlineStr"/>
+      <c r="AG386" s="2" t="inlineStr"/>
+      <c r="AH386" s="2" t="inlineStr"/>
+      <c r="AI386" s="2" t="inlineStr"/>
+      <c r="AJ386" s="2" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>85b9a7e1856e4dd8</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>0.55055</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="inlineStr"/>
+      <c r="N387" s="2" t="inlineStr"/>
+      <c r="O387" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P387" s="2" t="inlineStr"/>
+      <c r="Q387" s="2" t="inlineStr">
+        <is>
+          <t>0.01137949308755759</t>
+        </is>
+      </c>
+      <c r="R387" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:29.939077Z</t>
+        </is>
+      </c>
+      <c r="S387" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T387" s="2" t="inlineStr"/>
+      <c r="U387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr"/>
+      <c r="W387" s="2" t="inlineStr"/>
+      <c r="X387" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y387" s="2" t="inlineStr"/>
+      <c r="Z387" s="2" t="inlineStr"/>
+      <c r="AA387" s="2" t="inlineStr"/>
+      <c r="AB387" s="2" t="inlineStr"/>
+      <c r="AC387" s="2" t="inlineStr"/>
+      <c r="AD387" s="2" t="inlineStr"/>
+      <c r="AE387" s="2" t="inlineStr"/>
+      <c r="AF387" s="2" t="inlineStr"/>
+      <c r="AG387" s="2" t="inlineStr"/>
+      <c r="AH387" s="2" t="inlineStr"/>
+      <c r="AI387" s="2" t="inlineStr"/>
+      <c r="AJ387" s="2" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>55e8671b444242d1</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>68689</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K388" s="2" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>0.573934</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr"/>
+      <c r="O388" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P388" s="2" t="inlineStr"/>
+      <c r="Q388" s="2" t="inlineStr">
+        <is>
+          <t>-0.026066000000000034</t>
+        </is>
+      </c>
+      <c r="R388" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:30.477262Z</t>
+        </is>
+      </c>
+      <c r="S388" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T388" s="2" t="inlineStr"/>
+      <c r="U388" s="2" t="inlineStr"/>
+      <c r="V388" s="2" t="inlineStr"/>
+      <c r="W388" s="2" t="inlineStr"/>
+      <c r="X388" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y388" s="2" t="inlineStr"/>
+      <c r="Z388" s="2" t="inlineStr"/>
+      <c r="AA388" s="2" t="inlineStr"/>
+      <c r="AB388" s="2" t="inlineStr"/>
+      <c r="AC388" s="2" t="inlineStr"/>
+      <c r="AD388" s="2" t="inlineStr"/>
+      <c r="AE388" s="2" t="inlineStr"/>
+      <c r="AF388" s="2" t="inlineStr"/>
+      <c r="AG388" s="2" t="inlineStr"/>
+      <c r="AH388" s="2" t="inlineStr"/>
+      <c r="AI388" s="2" t="inlineStr"/>
+      <c r="AJ388" s="2" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>f6a1d3f3864848eb</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>68688</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K389" s="2" t="inlineStr"/>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>0.531003</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="inlineStr"/>
+      <c r="N389" s="2" t="inlineStr"/>
+      <c r="O389" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P389" s="2" t="inlineStr"/>
+      <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>-0.018546549549549485</t>
+        </is>
+      </c>
+      <c r="R389" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:31.160482Z</t>
+        </is>
+      </c>
+      <c r="S389" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="inlineStr"/>
+      <c r="V389" s="2" t="inlineStr"/>
+      <c r="W389" s="2" t="inlineStr"/>
+      <c r="X389" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y389" s="2" t="inlineStr"/>
+      <c r="Z389" s="2" t="inlineStr"/>
+      <c r="AA389" s="2" t="inlineStr"/>
+      <c r="AB389" s="2" t="inlineStr"/>
+      <c r="AC389" s="2" t="inlineStr"/>
+      <c r="AD389" s="2" t="inlineStr"/>
+      <c r="AE389" s="2" t="inlineStr"/>
+      <c r="AF389" s="2" t="inlineStr"/>
+      <c r="AG389" s="2" t="inlineStr"/>
+      <c r="AH389" s="2" t="inlineStr"/>
+      <c r="AI389" s="2" t="inlineStr"/>
+      <c r="AJ389" s="2" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>f8e46b6fc54e4b90</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K390" s="2" t="inlineStr"/>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>0.624143</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr"/>
+      <c r="O390" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P390" s="2" t="inlineStr"/>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>0.004371136882129312</t>
+        </is>
+      </c>
+      <c r="R390" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:34.284466Z</t>
+        </is>
+      </c>
+      <c r="S390" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T390" s="2" t="inlineStr"/>
+      <c r="U390" s="2" t="inlineStr"/>
+      <c r="V390" s="2" t="inlineStr"/>
+      <c r="W390" s="2" t="inlineStr"/>
+      <c r="X390" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y390" s="2" t="inlineStr"/>
+      <c r="Z390" s="2" t="inlineStr"/>
+      <c r="AA390" s="2" t="inlineStr"/>
+      <c r="AB390" s="2" t="inlineStr"/>
+      <c r="AC390" s="2" t="inlineStr"/>
+      <c r="AD390" s="2" t="inlineStr"/>
+      <c r="AE390" s="2" t="inlineStr"/>
+      <c r="AF390" s="2" t="inlineStr"/>
+      <c r="AG390" s="2" t="inlineStr"/>
+      <c r="AH390" s="2" t="inlineStr"/>
+      <c r="AI390" s="2" t="inlineStr"/>
+      <c r="AJ390" s="2" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>0f865a9fec0b4039</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>0.591618</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr"/>
+      <c r="O391" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="inlineStr"/>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>0.10142192156862745</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:34.823771Z</t>
+        </is>
+      </c>
+      <c r="S391" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T391" s="2" t="inlineStr"/>
+      <c r="U391" s="2" t="inlineStr"/>
+      <c r="V391" s="2" t="inlineStr"/>
+      <c r="W391" s="2" t="inlineStr"/>
+      <c r="X391" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y391" s="2" t="inlineStr"/>
+      <c r="Z391" s="2" t="inlineStr"/>
+      <c r="AA391" s="2" t="inlineStr"/>
+      <c r="AB391" s="2" t="inlineStr"/>
+      <c r="AC391" s="2" t="inlineStr"/>
+      <c r="AD391" s="2" t="inlineStr"/>
+      <c r="AE391" s="2" t="inlineStr"/>
+      <c r="AF391" s="2" t="inlineStr"/>
+      <c r="AG391" s="2" t="inlineStr"/>
+      <c r="AH391" s="2" t="inlineStr"/>
+      <c r="AI391" s="2" t="inlineStr"/>
+      <c r="AJ391" s="2" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>7f74cba1a5274e73</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>69141</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K392" s="2" t="inlineStr"/>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>0.649994</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr"/>
+      <c r="O392" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P392" s="2" t="inlineStr"/>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>-0.00035565034965034936</t>
+        </is>
+      </c>
+      <c r="R392" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:35.473901Z</t>
+        </is>
+      </c>
+      <c r="S392" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="inlineStr"/>
+      <c r="W392" s="2" t="inlineStr"/>
+      <c r="X392" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y392" s="2" t="inlineStr"/>
+      <c r="Z392" s="2" t="inlineStr"/>
+      <c r="AA392" s="2" t="inlineStr"/>
+      <c r="AB392" s="2" t="inlineStr"/>
+      <c r="AC392" s="2" t="inlineStr"/>
+      <c r="AD392" s="2" t="inlineStr"/>
+      <c r="AE392" s="2" t="inlineStr"/>
+      <c r="AF392" s="2" t="inlineStr"/>
+      <c r="AG392" s="2" t="inlineStr"/>
+      <c r="AH392" s="2" t="inlineStr"/>
+      <c r="AI392" s="2" t="inlineStr"/>
+      <c r="AJ392" s="2" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>c6a0c948412644d4</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>69234</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K393" s="2" t="inlineStr"/>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>0.51668</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="inlineStr"/>
+      <c r="N393" s="2" t="inlineStr"/>
+      <c r="O393" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P393" s="2" t="inlineStr"/>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>0.11668</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:35.928266Z</t>
+        </is>
+      </c>
+      <c r="S393" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T393" s="2" t="inlineStr"/>
+      <c r="U393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="inlineStr"/>
+      <c r="W393" s="2" t="inlineStr"/>
+      <c r="X393" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y393" s="2" t="inlineStr"/>
+      <c r="Z393" s="2" t="inlineStr"/>
+      <c r="AA393" s="2" t="inlineStr"/>
+      <c r="AB393" s="2" t="inlineStr"/>
+      <c r="AC393" s="2" t="inlineStr"/>
+      <c r="AD393" s="2" t="inlineStr"/>
+      <c r="AE393" s="2" t="inlineStr"/>
+      <c r="AF393" s="2" t="inlineStr"/>
+      <c r="AG393" s="2" t="inlineStr"/>
+      <c r="AH393" s="2" t="inlineStr"/>
+      <c r="AI393" s="2" t="inlineStr"/>
+      <c r="AJ393" s="2" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>40c72bd9b98946a0</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>69233</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K394" s="2" t="inlineStr"/>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>0.5725</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr"/>
+      <c r="O394" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P394" s="2" t="inlineStr"/>
+      <c r="Q394" s="2" t="inlineStr">
+        <is>
+          <t>0.2323639455782313</t>
+        </is>
+      </c>
+      <c r="R394" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:36.567095Z</t>
+        </is>
+      </c>
+      <c r="S394" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T394" s="2" t="inlineStr"/>
+      <c r="U394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="inlineStr"/>
+      <c r="W394" s="2" t="inlineStr"/>
+      <c r="X394" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y394" s="2" t="inlineStr"/>
+      <c r="Z394" s="2" t="inlineStr"/>
+      <c r="AA394" s="2" t="inlineStr"/>
+      <c r="AB394" s="2" t="inlineStr"/>
+      <c r="AC394" s="2" t="inlineStr"/>
+      <c r="AD394" s="2" t="inlineStr"/>
+      <c r="AE394" s="2" t="inlineStr"/>
+      <c r="AF394" s="2" t="inlineStr"/>
+      <c r="AG394" s="2" t="inlineStr"/>
+      <c r="AH394" s="2" t="inlineStr"/>
+      <c r="AI394" s="2" t="inlineStr"/>
+      <c r="AJ394" s="2" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>fdfd7ba84d414a3c</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>0.604656</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="inlineStr"/>
+      <c r="N395" s="2" t="inlineStr"/>
+      <c r="O395" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P395" s="2" t="inlineStr"/>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>0.06548549308755758</t>
+        </is>
+      </c>
+      <c r="R395" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:37.194950Z</t>
+        </is>
+      </c>
+      <c r="S395" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="inlineStr"/>
+      <c r="V395" s="2" t="inlineStr"/>
+      <c r="W395" s="2" t="inlineStr"/>
+      <c r="X395" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y395" s="2" t="inlineStr"/>
+      <c r="Z395" s="2" t="inlineStr"/>
+      <c r="AA395" s="2" t="inlineStr"/>
+      <c r="AB395" s="2" t="inlineStr"/>
+      <c r="AC395" s="2" t="inlineStr"/>
+      <c r="AD395" s="2" t="inlineStr"/>
+      <c r="AE395" s="2" t="inlineStr"/>
+      <c r="AF395" s="2" t="inlineStr"/>
+      <c r="AG395" s="2" t="inlineStr"/>
+      <c r="AH395" s="2" t="inlineStr"/>
+      <c r="AI395" s="2" t="inlineStr"/>
+      <c r="AJ395" s="2" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>718572ba632845ec</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>69304</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K396" s="2" t="inlineStr"/>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>0.546359</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="inlineStr"/>
+      <c r="N396" s="2" t="inlineStr"/>
+      <c r="O396" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P396" s="2" t="inlineStr"/>
+      <c r="Q396" s="2" t="inlineStr">
+        <is>
+          <t>-0.013112365638766499</t>
+        </is>
+      </c>
+      <c r="R396" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:37.736771Z</t>
+        </is>
+      </c>
+      <c r="S396" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="inlineStr"/>
+      <c r="V396" s="2" t="inlineStr"/>
+      <c r="W396" s="2" t="inlineStr"/>
+      <c r="X396" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y396" s="2" t="inlineStr"/>
+      <c r="Z396" s="2" t="inlineStr"/>
+      <c r="AA396" s="2" t="inlineStr"/>
+      <c r="AB396" s="2" t="inlineStr"/>
+      <c r="AC396" s="2" t="inlineStr"/>
+      <c r="AD396" s="2" t="inlineStr"/>
+      <c r="AE396" s="2" t="inlineStr"/>
+      <c r="AF396" s="2" t="inlineStr"/>
+      <c r="AG396" s="2" t="inlineStr"/>
+      <c r="AH396" s="2" t="inlineStr"/>
+      <c r="AI396" s="2" t="inlineStr"/>
+      <c r="AJ396" s="2" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>e26917bfca6548bd</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>69507</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K397" s="2" t="inlineStr"/>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>0.638913</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="inlineStr"/>
+      <c r="N397" s="2" t="inlineStr"/>
+      <c r="O397" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P397" s="2" t="inlineStr"/>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>0.05908106722689077</t>
+        </is>
+      </c>
+      <c r="R397" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:38.863908Z</t>
+        </is>
+      </c>
+      <c r="S397" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T397" s="2" t="inlineStr"/>
+      <c r="U397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="inlineStr"/>
+      <c r="W397" s="2" t="inlineStr"/>
+      <c r="X397" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y397" s="2" t="inlineStr"/>
+      <c r="Z397" s="2" t="inlineStr"/>
+      <c r="AA397" s="2" t="inlineStr"/>
+      <c r="AB397" s="2" t="inlineStr"/>
+      <c r="AC397" s="2" t="inlineStr"/>
+      <c r="AD397" s="2" t="inlineStr"/>
+      <c r="AE397" s="2" t="inlineStr"/>
+      <c r="AF397" s="2" t="inlineStr"/>
+      <c r="AG397" s="2" t="inlineStr"/>
+      <c r="AH397" s="2" t="inlineStr"/>
+      <c r="AI397" s="2" t="inlineStr"/>
+      <c r="AJ397" s="2" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>c20d617316bb46e1</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>69506</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K398" s="2" t="inlineStr"/>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>0.597302</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="inlineStr"/>
+      <c r="N398" s="2" t="inlineStr"/>
+      <c r="O398" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P398" s="2" t="inlineStr"/>
+      <c r="Q398" s="2" t="inlineStr">
+        <is>
+          <t>0.1874659344262295</t>
+        </is>
+      </c>
+      <c r="R398" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:39.338315Z</t>
+        </is>
+      </c>
+      <c r="S398" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T398" s="2" t="inlineStr"/>
+      <c r="U398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="inlineStr"/>
+      <c r="W398" s="2" t="inlineStr"/>
+      <c r="X398" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y398" s="2" t="inlineStr"/>
+      <c r="Z398" s="2" t="inlineStr"/>
+      <c r="AA398" s="2" t="inlineStr"/>
+      <c r="AB398" s="2" t="inlineStr"/>
+      <c r="AC398" s="2" t="inlineStr"/>
+      <c r="AD398" s="2" t="inlineStr"/>
+      <c r="AE398" s="2" t="inlineStr"/>
+      <c r="AF398" s="2" t="inlineStr"/>
+      <c r="AG398" s="2" t="inlineStr"/>
+      <c r="AH398" s="2" t="inlineStr"/>
+      <c r="AI398" s="2" t="inlineStr"/>
+      <c r="AJ398" s="2" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>0e2401a1fe93481d</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>69512</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K399" s="2" t="inlineStr"/>
+      <c r="L399" s="2" t="inlineStr">
+        <is>
+          <t>0.739915</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="inlineStr"/>
+      <c r="N399" s="2" t="inlineStr"/>
+      <c r="O399" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P399" s="2" t="inlineStr"/>
+      <c r="Q399" s="2" t="inlineStr">
+        <is>
+          <t>0.04951252321981425</t>
+        </is>
+      </c>
+      <c r="R399" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:39.828051Z</t>
+        </is>
+      </c>
+      <c r="S399" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="inlineStr"/>
+      <c r="V399" s="2" t="inlineStr"/>
+      <c r="W399" s="2" t="inlineStr"/>
+      <c r="X399" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y399" s="2" t="inlineStr"/>
+      <c r="Z399" s="2" t="inlineStr"/>
+      <c r="AA399" s="2" t="inlineStr"/>
+      <c r="AB399" s="2" t="inlineStr"/>
+      <c r="AC399" s="2" t="inlineStr"/>
+      <c r="AD399" s="2" t="inlineStr"/>
+      <c r="AE399" s="2" t="inlineStr"/>
+      <c r="AF399" s="2" t="inlineStr"/>
+      <c r="AG399" s="2" t="inlineStr"/>
+      <c r="AH399" s="2" t="inlineStr"/>
+      <c r="AI399" s="2" t="inlineStr"/>
+      <c r="AJ399" s="2" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>ac1e63da1f424fd6</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>69511</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K400" s="2" t="inlineStr"/>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>0.699554</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr"/>
+      <c r="N400" s="2" t="inlineStr"/>
+      <c r="O400" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P400" s="2" t="inlineStr"/>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>0.09017900000000001</t>
+        </is>
+      </c>
+      <c r="R400" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:40.294698Z</t>
+        </is>
+      </c>
+      <c r="S400" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="inlineStr"/>
+      <c r="V400" s="2" t="inlineStr"/>
+      <c r="W400" s="2" t="inlineStr"/>
+      <c r="X400" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y400" s="2" t="inlineStr"/>
+      <c r="Z400" s="2" t="inlineStr"/>
+      <c r="AA400" s="2" t="inlineStr"/>
+      <c r="AB400" s="2" t="inlineStr"/>
+      <c r="AC400" s="2" t="inlineStr"/>
+      <c r="AD400" s="2" t="inlineStr"/>
+      <c r="AE400" s="2" t="inlineStr"/>
+      <c r="AF400" s="2" t="inlineStr"/>
+      <c r="AG400" s="2" t="inlineStr"/>
+      <c r="AH400" s="2" t="inlineStr"/>
+      <c r="AI400" s="2" t="inlineStr"/>
+      <c r="AJ400" s="2" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>145252a3528a442e</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>69539</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K401" s="2" t="inlineStr"/>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>0.637225</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="inlineStr"/>
+      <c r="N401" s="2" t="inlineStr"/>
+      <c r="O401" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P401" s="2" t="inlineStr"/>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>0.0777536343612335</t>
+        </is>
+      </c>
+      <c r="R401" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:41.252699Z</t>
+        </is>
+      </c>
+      <c r="S401" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T401" s="2" t="inlineStr"/>
+      <c r="U401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="inlineStr"/>
+      <c r="W401" s="2" t="inlineStr"/>
+      <c r="X401" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y401" s="2" t="inlineStr"/>
+      <c r="Z401" s="2" t="inlineStr"/>
+      <c r="AA401" s="2" t="inlineStr"/>
+      <c r="AB401" s="2" t="inlineStr"/>
+      <c r="AC401" s="2" t="inlineStr"/>
+      <c r="AD401" s="2" t="inlineStr"/>
+      <c r="AE401" s="2" t="inlineStr"/>
+      <c r="AF401" s="2" t="inlineStr"/>
+      <c r="AG401" s="2" t="inlineStr"/>
+      <c r="AH401" s="2" t="inlineStr"/>
+      <c r="AI401" s="2" t="inlineStr"/>
+      <c r="AJ401" s="2" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>342a191cf6af432f</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>0.665588</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr"/>
+      <c r="N402" s="2" t="inlineStr"/>
+      <c r="O402" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P402" s="2" t="inlineStr"/>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>0.045816136882129266</t>
+        </is>
+      </c>
+      <c r="R402" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:44.546269Z</t>
+        </is>
+      </c>
+      <c r="S402" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="inlineStr"/>
+      <c r="W402" s="2" t="inlineStr"/>
+      <c r="X402" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y402" s="2" t="inlineStr"/>
+      <c r="Z402" s="2" t="inlineStr"/>
+      <c r="AA402" s="2" t="inlineStr"/>
+      <c r="AB402" s="2" t="inlineStr"/>
+      <c r="AC402" s="2" t="inlineStr"/>
+      <c r="AD402" s="2" t="inlineStr"/>
+      <c r="AE402" s="2" t="inlineStr"/>
+      <c r="AF402" s="2" t="inlineStr"/>
+      <c r="AG402" s="2" t="inlineStr"/>
+      <c r="AH402" s="2" t="inlineStr"/>
+      <c r="AI402" s="2" t="inlineStr"/>
+      <c r="AJ402" s="2" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>9bcbd74347cf434c</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>0.561203</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr"/>
+      <c r="N403" s="2" t="inlineStr"/>
+      <c r="O403" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P403" s="2" t="inlineStr"/>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>0.12067436563876655</t>
+        </is>
+      </c>
+      <c r="R403" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:46.445811Z</t>
+        </is>
+      </c>
+      <c r="S403" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T403" s="2" t="inlineStr"/>
+      <c r="U403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="inlineStr"/>
+      <c r="W403" s="2" t="inlineStr"/>
+      <c r="X403" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y403" s="2" t="inlineStr"/>
+      <c r="Z403" s="2" t="inlineStr"/>
+      <c r="AA403" s="2" t="inlineStr"/>
+      <c r="AB403" s="2" t="inlineStr"/>
+      <c r="AC403" s="2" t="inlineStr"/>
+      <c r="AD403" s="2" t="inlineStr"/>
+      <c r="AE403" s="2" t="inlineStr"/>
+      <c r="AF403" s="2" t="inlineStr"/>
+      <c r="AG403" s="2" t="inlineStr"/>
+      <c r="AH403" s="2" t="inlineStr"/>
+      <c r="AI403" s="2" t="inlineStr"/>
+      <c r="AJ403" s="2" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>d96ab9a5cef5438a</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K404" s="2" t="inlineStr"/>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>0.832591</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr"/>
+      <c r="N404" s="2" t="inlineStr"/>
+      <c r="O404" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P404" s="2" t="inlineStr"/>
+      <c r="Q404" s="2" t="inlineStr">
+        <is>
+          <t>0.24242706557377047</t>
+        </is>
+      </c>
+      <c r="R404" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:47.442405Z</t>
+        </is>
+      </c>
+      <c r="S404" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T404" s="2" t="inlineStr"/>
+      <c r="U404" s="2" t="inlineStr"/>
+      <c r="V404" s="2" t="inlineStr"/>
+      <c r="W404" s="2" t="inlineStr"/>
+      <c r="X404" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y404" s="2" t="inlineStr"/>
+      <c r="Z404" s="2" t="inlineStr"/>
+      <c r="AA404" s="2" t="inlineStr"/>
+      <c r="AB404" s="2" t="inlineStr"/>
+      <c r="AC404" s="2" t="inlineStr"/>
+      <c r="AD404" s="2" t="inlineStr"/>
+      <c r="AE404" s="2" t="inlineStr"/>
+      <c r="AF404" s="2" t="inlineStr"/>
+      <c r="AG404" s="2" t="inlineStr"/>
+      <c r="AH404" s="2" t="inlineStr"/>
+      <c r="AI404" s="2" t="inlineStr"/>
+      <c r="AJ404" s="2" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>59037255ef574a83</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K405" s="2" t="inlineStr"/>
+      <c r="L405" s="2" t="inlineStr">
+        <is>
+          <t>0.577055</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="inlineStr"/>
+      <c r="N405" s="2" t="inlineStr"/>
+      <c r="O405" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P405" s="2" t="inlineStr"/>
+      <c r="Q405" s="2" t="inlineStr">
+        <is>
+          <t>0.07705499999999998</t>
+        </is>
+      </c>
+      <c r="R405" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:47.949141Z</t>
+        </is>
+      </c>
+      <c r="S405" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T405" s="2" t="inlineStr"/>
+      <c r="U405" s="2" t="inlineStr"/>
+      <c r="V405" s="2" t="inlineStr"/>
+      <c r="W405" s="2" t="inlineStr"/>
+      <c r="X405" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y405" s="2" t="inlineStr"/>
+      <c r="Z405" s="2" t="inlineStr"/>
+      <c r="AA405" s="2" t="inlineStr"/>
+      <c r="AB405" s="2" t="inlineStr"/>
+      <c r="AC405" s="2" t="inlineStr"/>
+      <c r="AD405" s="2" t="inlineStr"/>
+      <c r="AE405" s="2" t="inlineStr"/>
+      <c r="AF405" s="2" t="inlineStr"/>
+      <c r="AG405" s="2" t="inlineStr"/>
+      <c r="AH405" s="2" t="inlineStr"/>
+      <c r="AI405" s="2" t="inlineStr"/>
+      <c r="AJ405" s="2" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>4e9b190cd69444ed</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>69930</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K406" s="2" t="inlineStr"/>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>0.536006</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="inlineStr"/>
+      <c r="N406" s="2" t="inlineStr"/>
+      <c r="O406" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P406" s="2" t="inlineStr"/>
+      <c r="Q406" s="2" t="inlineStr">
+        <is>
+          <t>0.08555554954954947</t>
+        </is>
+      </c>
+      <c r="R406" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:48.438562Z</t>
+        </is>
+      </c>
+      <c r="S406" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T406" s="2" t="inlineStr"/>
+      <c r="U406" s="2" t="inlineStr"/>
+      <c r="V406" s="2" t="inlineStr"/>
+      <c r="W406" s="2" t="inlineStr"/>
+      <c r="X406" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y406" s="2" t="inlineStr"/>
+      <c r="Z406" s="2" t="inlineStr"/>
+      <c r="AA406" s="2" t="inlineStr"/>
+      <c r="AB406" s="2" t="inlineStr"/>
+      <c r="AC406" s="2" t="inlineStr"/>
+      <c r="AD406" s="2" t="inlineStr"/>
+      <c r="AE406" s="2" t="inlineStr"/>
+      <c r="AF406" s="2" t="inlineStr"/>
+      <c r="AG406" s="2" t="inlineStr"/>
+      <c r="AH406" s="2" t="inlineStr"/>
+      <c r="AI406" s="2" t="inlineStr"/>
+      <c r="AJ406" s="2" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>045bc5c3883c4172</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>69948</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K407" s="2" t="inlineStr"/>
+      <c r="L407" s="2" t="inlineStr">
+        <is>
+          <t>0.564089</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="inlineStr"/>
+      <c r="N407" s="2" t="inlineStr"/>
+      <c r="O407" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P407" s="2" t="inlineStr"/>
+      <c r="Q407" s="2" t="inlineStr">
+        <is>
+          <t>-0.10587799669967002</t>
+        </is>
+      </c>
+      <c r="R407" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:49.352813Z</t>
+        </is>
+      </c>
+      <c r="S407" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="inlineStr"/>
+      <c r="V407" s="2" t="inlineStr"/>
+      <c r="W407" s="2" t="inlineStr"/>
+      <c r="X407" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y407" s="2" t="inlineStr"/>
+      <c r="Z407" s="2" t="inlineStr"/>
+      <c r="AA407" s="2" t="inlineStr"/>
+      <c r="AB407" s="2" t="inlineStr"/>
+      <c r="AC407" s="2" t="inlineStr"/>
+      <c r="AD407" s="2" t="inlineStr"/>
+      <c r="AE407" s="2" t="inlineStr"/>
+      <c r="AF407" s="2" t="inlineStr"/>
+      <c r="AG407" s="2" t="inlineStr"/>
+      <c r="AH407" s="2" t="inlineStr"/>
+      <c r="AI407" s="2" t="inlineStr"/>
+      <c r="AJ407" s="2" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>6c24e9b6071446c3</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>69949</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K408" s="2" t="inlineStr"/>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>0.530192</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="inlineStr"/>
+      <c r="N408" s="2" t="inlineStr"/>
+      <c r="O408" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P408" s="2" t="inlineStr"/>
+      <c r="Q408" s="2" t="inlineStr">
+        <is>
+          <t>0.06936250691244239</t>
+        </is>
+      </c>
+      <c r="R408" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:49.832690Z</t>
+        </is>
+      </c>
+      <c r="S408" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="inlineStr"/>
+      <c r="V408" s="2" t="inlineStr"/>
+      <c r="W408" s="2" t="inlineStr"/>
+      <c r="X408" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y408" s="2" t="inlineStr"/>
+      <c r="Z408" s="2" t="inlineStr"/>
+      <c r="AA408" s="2" t="inlineStr"/>
+      <c r="AB408" s="2" t="inlineStr"/>
+      <c r="AC408" s="2" t="inlineStr"/>
+      <c r="AD408" s="2" t="inlineStr"/>
+      <c r="AE408" s="2" t="inlineStr"/>
+      <c r="AF408" s="2" t="inlineStr"/>
+      <c r="AG408" s="2" t="inlineStr"/>
+      <c r="AH408" s="2" t="inlineStr"/>
+      <c r="AI408" s="2" t="inlineStr"/>
+      <c r="AJ408" s="2" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>6ccd597ae9b24457</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>69950</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K409" s="2" t="inlineStr"/>
+      <c r="L409" s="2" t="inlineStr">
+        <is>
+          <t>0.534563</t>
+        </is>
+      </c>
+      <c r="M409" s="2" t="inlineStr"/>
+      <c r="N409" s="2" t="inlineStr"/>
+      <c r="O409" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P409" s="2" t="inlineStr"/>
+      <c r="Q409" s="2" t="inlineStr">
+        <is>
+          <t>-0.04526893277310917</t>
+        </is>
+      </c>
+      <c r="R409" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:50.326365Z</t>
+        </is>
+      </c>
+      <c r="S409" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T409" s="2" t="inlineStr"/>
+      <c r="U409" s="2" t="inlineStr"/>
+      <c r="V409" s="2" t="inlineStr"/>
+      <c r="W409" s="2" t="inlineStr"/>
+      <c r="X409" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y409" s="2" t="inlineStr"/>
+      <c r="Z409" s="2" t="inlineStr"/>
+      <c r="AA409" s="2" t="inlineStr"/>
+      <c r="AB409" s="2" t="inlineStr"/>
+      <c r="AC409" s="2" t="inlineStr"/>
+      <c r="AD409" s="2" t="inlineStr"/>
+      <c r="AE409" s="2" t="inlineStr"/>
+      <c r="AF409" s="2" t="inlineStr"/>
+      <c r="AG409" s="2" t="inlineStr"/>
+      <c r="AH409" s="2" t="inlineStr"/>
+      <c r="AI409" s="2" t="inlineStr"/>
+      <c r="AJ409" s="2" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>e2c7780d4c204b34</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>69951</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K410" s="2" t="inlineStr"/>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>0.516071</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="inlineStr"/>
+      <c r="N410" s="2" t="inlineStr"/>
+      <c r="O410" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P410" s="2" t="inlineStr"/>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>0.13584286311787064</t>
+        </is>
+      </c>
+      <c r="R410" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:50.827783Z</t>
+        </is>
+      </c>
+      <c r="S410" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="inlineStr"/>
+      <c r="U410" s="2" t="inlineStr"/>
+      <c r="V410" s="2" t="inlineStr"/>
+      <c r="W410" s="2" t="inlineStr"/>
+      <c r="X410" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y410" s="2" t="inlineStr"/>
+      <c r="Z410" s="2" t="inlineStr"/>
+      <c r="AA410" s="2" t="inlineStr"/>
+      <c r="AB410" s="2" t="inlineStr"/>
+      <c r="AC410" s="2" t="inlineStr"/>
+      <c r="AD410" s="2" t="inlineStr"/>
+      <c r="AE410" s="2" t="inlineStr"/>
+      <c r="AF410" s="2" t="inlineStr"/>
+      <c r="AG410" s="2" t="inlineStr"/>
+      <c r="AH410" s="2" t="inlineStr"/>
+      <c r="AI410" s="2" t="inlineStr"/>
+      <c r="AJ410" s="2" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>de668e26e2614503</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K411" s="2" t="inlineStr"/>
+      <c r="L411" s="2" t="inlineStr">
+        <is>
+          <t>0.607498</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="inlineStr"/>
+      <c r="N411" s="2" t="inlineStr"/>
+      <c r="O411" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P411" s="2" t="inlineStr"/>
+      <c r="Q411" s="2" t="inlineStr">
+        <is>
+          <t>0.08826723076923082</t>
+        </is>
+      </c>
+      <c r="R411" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:51.809850Z</t>
+        </is>
+      </c>
+      <c r="S411" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T411" s="2" t="inlineStr"/>
+      <c r="U411" s="2" t="inlineStr"/>
+      <c r="V411" s="2" t="inlineStr"/>
+      <c r="W411" s="2" t="inlineStr"/>
+      <c r="X411" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y411" s="2" t="inlineStr"/>
+      <c r="Z411" s="2" t="inlineStr"/>
+      <c r="AA411" s="2" t="inlineStr"/>
+      <c r="AB411" s="2" t="inlineStr"/>
+      <c r="AC411" s="2" t="inlineStr"/>
+      <c r="AD411" s="2" t="inlineStr"/>
+      <c r="AE411" s="2" t="inlineStr"/>
+      <c r="AF411" s="2" t="inlineStr"/>
+      <c r="AG411" s="2" t="inlineStr"/>
+      <c r="AH411" s="2" t="inlineStr"/>
+      <c r="AI411" s="2" t="inlineStr"/>
+      <c r="AJ411" s="2" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>942770d640114038</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>70302</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="inlineStr"/>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>0.535928</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr"/>
+      <c r="N412" s="2" t="inlineStr"/>
+      <c r="O412" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P412" s="2" t="inlineStr"/>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>-0.0032425069124424333</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:52.802307Z</t>
+        </is>
+      </c>
+      <c r="S412" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
+      <c r="V412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="inlineStr"/>
+      <c r="X412" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y412" s="2" t="inlineStr"/>
+      <c r="Z412" s="2" t="inlineStr"/>
+      <c r="AA412" s="2" t="inlineStr"/>
+      <c r="AB412" s="2" t="inlineStr"/>
+      <c r="AC412" s="2" t="inlineStr"/>
+      <c r="AD412" s="2" t="inlineStr"/>
+      <c r="AE412" s="2" t="inlineStr"/>
+      <c r="AF412" s="2" t="inlineStr"/>
+      <c r="AG412" s="2" t="inlineStr"/>
+      <c r="AH412" s="2" t="inlineStr"/>
+      <c r="AI412" s="2" t="inlineStr"/>
+      <c r="AJ412" s="2" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>f77030c0c6e94777</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>70349</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K413" s="2" t="inlineStr"/>
+      <c r="L413" s="2" t="inlineStr">
+        <is>
+          <t>0.649617</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="inlineStr"/>
+      <c r="N413" s="2" t="inlineStr"/>
+      <c r="O413" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P413" s="2" t="inlineStr"/>
+      <c r="Q413" s="2" t="inlineStr">
+        <is>
+          <t>-0.030894182108626156</t>
+        </is>
+      </c>
+      <c r="R413" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:53.928842Z</t>
+        </is>
+      </c>
+      <c r="S413" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T413" s="2" t="inlineStr"/>
+      <c r="U413" s="2" t="inlineStr"/>
+      <c r="V413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+      <c r="X413" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y413" s="2" t="inlineStr"/>
+      <c r="Z413" s="2" t="inlineStr"/>
+      <c r="AA413" s="2" t="inlineStr"/>
+      <c r="AB413" s="2" t="inlineStr"/>
+      <c r="AC413" s="2" t="inlineStr"/>
+      <c r="AD413" s="2" t="inlineStr"/>
+      <c r="AE413" s="2" t="inlineStr"/>
+      <c r="AF413" s="2" t="inlineStr"/>
+      <c r="AG413" s="2" t="inlineStr"/>
+      <c r="AH413" s="2" t="inlineStr"/>
+      <c r="AI413" s="2" t="inlineStr"/>
+      <c r="AJ413" s="2" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>40c9d0b834ae44dc</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>70348</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K414" s="2" t="inlineStr"/>
+      <c r="L414" s="2" t="inlineStr">
+        <is>
+          <t>0.500208</t>
+        </is>
+      </c>
+      <c r="M414" s="2" t="inlineStr"/>
+      <c r="N414" s="2" t="inlineStr"/>
+      <c r="O414" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P414" s="2" t="inlineStr"/>
+      <c r="Q414" s="2" t="inlineStr">
+        <is>
+          <t>-0.1195638631178707</t>
+        </is>
+      </c>
+      <c r="R414" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:54.377453Z</t>
+        </is>
+      </c>
+      <c r="S414" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+      <c r="X414" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y414" s="2" t="inlineStr"/>
+      <c r="Z414" s="2" t="inlineStr"/>
+      <c r="AA414" s="2" t="inlineStr"/>
+      <c r="AB414" s="2" t="inlineStr"/>
+      <c r="AC414" s="2" t="inlineStr"/>
+      <c r="AD414" s="2" t="inlineStr"/>
+      <c r="AE414" s="2" t="inlineStr"/>
+      <c r="AF414" s="2" t="inlineStr"/>
+      <c r="AG414" s="2" t="inlineStr"/>
+      <c r="AH414" s="2" t="inlineStr"/>
+      <c r="AI414" s="2" t="inlineStr"/>
+      <c r="AJ414" s="2" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>e0277863332f4f2e</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K415" s="2" t="inlineStr"/>
+      <c r="L415" s="2" t="inlineStr">
+        <is>
+          <t>0.566884</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="inlineStr"/>
+      <c r="N415" s="2" t="inlineStr"/>
+      <c r="O415" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P415" s="2" t="inlineStr"/>
+      <c r="Q415" s="2" t="inlineStr">
+        <is>
+          <t>0.13769945064377687</t>
+        </is>
+      </c>
+      <c r="R415" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:54.874184Z</t>
+        </is>
+      </c>
+      <c r="S415" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T415" s="2" t="inlineStr"/>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
+      <c r="X415" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y415" s="2" t="inlineStr"/>
+      <c r="Z415" s="2" t="inlineStr"/>
+      <c r="AA415" s="2" t="inlineStr"/>
+      <c r="AB415" s="2" t="inlineStr"/>
+      <c r="AC415" s="2" t="inlineStr"/>
+      <c r="AD415" s="2" t="inlineStr"/>
+      <c r="AE415" s="2" t="inlineStr"/>
+      <c r="AF415" s="2" t="inlineStr"/>
+      <c r="AG415" s="2" t="inlineStr"/>
+      <c r="AH415" s="2" t="inlineStr"/>
+      <c r="AI415" s="2" t="inlineStr"/>
+      <c r="AJ415" s="2" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>abb6a986c25b4eac</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>70454</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K416" s="2" t="inlineStr"/>
+      <c r="L416" s="2" t="inlineStr">
+        <is>
+          <t>0.515927</t>
+        </is>
+      </c>
+      <c r="M416" s="2" t="inlineStr"/>
+      <c r="N416" s="2" t="inlineStr"/>
+      <c r="O416" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P416" s="2" t="inlineStr"/>
+      <c r="Q416" s="2" t="inlineStr">
+        <is>
+          <t>-0.10384486311787067</t>
+        </is>
+      </c>
+      <c r="R416" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.920586Z</t>
+        </is>
+      </c>
+      <c r="S416" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T416" s="2" t="inlineStr"/>
+      <c r="U416" s="2" t="inlineStr"/>
+      <c r="V416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
+      <c r="X416" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y416" s="2" t="inlineStr"/>
+      <c r="Z416" s="2" t="inlineStr"/>
+      <c r="AA416" s="2" t="inlineStr"/>
+      <c r="AB416" s="2" t="inlineStr"/>
+      <c r="AC416" s="2" t="inlineStr"/>
+      <c r="AD416" s="2" t="inlineStr"/>
+      <c r="AE416" s="2" t="inlineStr"/>
+      <c r="AF416" s="2" t="inlineStr"/>
+      <c r="AG416" s="2" t="inlineStr"/>
+      <c r="AH416" s="2" t="inlineStr"/>
+      <c r="AI416" s="2" t="inlineStr"/>
+      <c r="AJ416" s="2" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>e2b896f1e3cc4538</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K417" s="2" t="inlineStr"/>
+      <c r="L417" s="2" t="inlineStr">
+        <is>
+          <t>0.590765</t>
+        </is>
+      </c>
+      <c r="M417" s="2" t="inlineStr"/>
+      <c r="N417" s="2" t="inlineStr"/>
+      <c r="O417" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P417" s="2" t="inlineStr"/>
+      <c r="Q417" s="2" t="inlineStr">
+        <is>
+          <t>0.019949549356223173</t>
+        </is>
+      </c>
+      <c r="R417" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469425Z</t>
+        </is>
+      </c>
+      <c r="S417" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T417" s="2" t="inlineStr"/>
+      <c r="U417" s="2" t="inlineStr"/>
+      <c r="V417" s="2" t="inlineStr"/>
+      <c r="W417" s="2" t="inlineStr"/>
+      <c r="X417" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y417" s="2" t="inlineStr"/>
+      <c r="Z417" s="2" t="inlineStr"/>
+      <c r="AA417" s="2" t="inlineStr"/>
+      <c r="AB417" s="2" t="inlineStr"/>
+      <c r="AC417" s="2" t="inlineStr"/>
+      <c r="AD417" s="2" t="inlineStr"/>
+      <c r="AE417" s="2" t="inlineStr"/>
+      <c r="AF417" s="2" t="inlineStr"/>
+      <c r="AG417" s="2" t="inlineStr"/>
+      <c r="AH417" s="2" t="inlineStr"/>
+      <c r="AI417" s="2" t="inlineStr"/>
+      <c r="AJ417" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ337"/>
+  <autoFilter ref="A1:AJ417"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>